--- a/public/artworks.xlsx
+++ b/public/artworks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\dev\artbook\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DDB1C3-E790-485C-9EA7-C6F4EF17BD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0200EEF1-89B6-420E-B6EA-B0AFCD0EAF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="450">
   <si>
     <t>title</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>impressionnisme</t>
-  </si>
-  <si>
-    <t>monet_1898.jpeg</t>
   </si>
   <si>
     <t>Intérieur d'une église à Utrecht</t>
@@ -72,9 +69,6 @@
 </t>
   </si>
   <si>
-    <t>saenredam_1644.jpg</t>
-  </si>
-  <si>
     <t>L'École d'Athènes</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
     <t>cinquecento, renaissance</t>
   </si>
   <si>
-    <t>raphael_1509.webp</t>
-  </si>
-  <si>
     <t>Marat assassiné</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
     <t>neoclassicisme</t>
   </si>
   <si>
-    <t>david_1793.jpg</t>
-  </si>
-  <si>
     <t>Guernica</t>
   </si>
   <si>
@@ -108,25 +96,10 @@
     <t>cubisme</t>
   </si>
   <si>
-    <t>picasso_1937.avif</t>
-  </si>
-  <si>
-    <t>Christ Pantocrator de Daphni</t>
-  </si>
-  <si>
     <t>Inconnu</t>
   </si>
   <si>
     <t>moyen-âge, byzantin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christ Pantocrator : représentation artistique de Jésus Christ dans son
-corps glorieux par opposition aux représentations plus humaines du Christ
-souffrant la Passion sur la Croix, ou celle de l'Enfant-Jésus
-</t>
-  </si>
-  <si>
-    <t>pantocrator_1090.jpg</t>
   </si>
   <si>
     <t>Madone Rucellai</t>
@@ -143,9 +116,6 @@
 </t>
   </si>
   <si>
-    <t>duccio_1285.jpg</t>
-  </si>
-  <si>
     <t>Noël, la crèche à Greccio</t>
   </si>
   <si>
@@ -155,9 +125,6 @@
     <t>moyen-âge</t>
   </si>
   <si>
-    <t>giotto_1297.webp</t>
-  </si>
-  <si>
     <t>Saint Georges</t>
   </si>
   <si>
@@ -165,18 +132,6 @@
   </si>
   <si>
     <t>quattrocento</t>
-  </si>
-  <si>
-    <t>donatello_1415.jpg</t>
-  </si>
-  <si>
-    <t>La Bataille de San Romano</t>
-  </si>
-  <si>
-    <t>Paolo Uccello</t>
-  </si>
-  <si>
-    <t>uccello_1456.jpg</t>
   </si>
   <si>
     <t>La Naissance de Vénus</t>
@@ -191,9 +146,6 @@
 </t>
   </si>
   <si>
-    <t>botticelli_1482.webp</t>
-  </si>
-  <si>
     <t>La Joconde</t>
   </si>
   <si>
@@ -206,9 +158,6 @@
 </t>
   </si>
   <si>
-    <t>da_vinci_1503.jpg</t>
-  </si>
-  <si>
     <t>La Création d'Adam</t>
   </si>
   <si>
@@ -220,9 +169,6 @@
 </t>
   </si>
   <si>
-    <t>michelange_1512.jpg</t>
-  </si>
-  <si>
     <t>La Sainte Famille de François Ier</t>
   </si>
   <si>
@@ -231,13 +177,7 @@
 </t>
   </si>
   <si>
-    <t>raphael_1518.jpg</t>
-  </si>
-  <si>
     <t>Saint Michel terrassant le démon</t>
-  </si>
-  <si>
-    <t>raphael_1519.jpg</t>
   </si>
   <si>
     <t>Portrait de Christine de Danemark</t>
@@ -255,9 +195,6 @@
 </t>
   </si>
   <si>
-    <t>holbein_1538.jpg</t>
-  </si>
-  <si>
     <t>La Danse des paysans</t>
   </si>
   <si>
@@ -270,9 +207,6 @@
 </t>
   </si>
   <si>
-    <t>brueghel_1568.jpg</t>
-  </si>
-  <si>
     <t>La Tour de Babel</t>
   </si>
   <si>
@@ -282,9 +216,6 @@
 </t>
   </si>
   <si>
-    <t>brueghel_1563.webp</t>
-  </si>
-  <si>
     <t>Le Martyre de saint Matthieu</t>
   </si>
   <si>
@@ -299,13 +230,7 @@
 </t>
   </si>
   <si>
-    <t>caravage_1600.jpg</t>
-  </si>
-  <si>
     <t>La Mise au tombeau</t>
-  </si>
-  <si>
-    <t>caravage_1603.jpg</t>
   </si>
   <si>
     <t>Baldaquin de Saint Pierre</t>
@@ -319,31 +244,19 @@
 </t>
   </si>
   <si>
-    <t>bernini_1633.jpg</t>
-  </si>
-  <si>
     <t>L'Extase de sainte Thérèse</t>
   </si>
   <si>
-    <t>bernini_1652.jpg</t>
-  </si>
-  <si>
     <t>Portrait de Pieter van den Broecke</t>
   </si>
   <si>
     <t>Frans Hals</t>
   </si>
   <si>
-    <t>hals_1633.jpg</t>
-  </si>
-  <si>
     <t>Nature morte aux citrons et oranges avec une rose</t>
   </si>
   <si>
     <t>Francisco de Zurbarán</t>
-  </si>
-  <si>
-    <t>zurbaran_1633.jpg</t>
   </si>
   <si>
     <t>Le Jugement de Salomon</t>
@@ -366,27 +279,18 @@
 </t>
   </si>
   <si>
-    <t>poussin_1649.jpg</t>
-  </si>
-  <si>
     <t>Triomphe du nom de Jésus</t>
   </si>
   <si>
     <t>Giovanni Battista Gaulli</t>
   </si>
   <si>
-    <t>gaulli_1670.jpg</t>
-  </si>
-  <si>
     <t>Moïse défendant les filles de Jethro</t>
   </si>
   <si>
     <t>Charles Le Brun</t>
   </si>
   <si>
-    <t>lebrun_1686.jpg</t>
-  </si>
-  <si>
     <t>L'Embarquement pour Cythère</t>
   </si>
   <si>
@@ -396,18 +300,12 @@
     <t>rococo</t>
   </si>
   <si>
-    <t>watteau_1718.jpg</t>
-  </si>
-  <si>
     <t>La Raie</t>
   </si>
   <si>
     <t>Jean Siméon Chardin</t>
   </si>
   <si>
-    <t>chardin_1728.jpg</t>
-  </si>
-  <si>
     <t>Ruines Antiques</t>
   </si>
   <si>
@@ -417,9 +315,6 @@
     <t>classicisme, neoclassicisme</t>
   </si>
   <si>
-    <t>servandoni_1731.jpg</t>
-  </si>
-  <si>
     <t>La Carrière d'une prostituée</t>
   </si>
   <si>
@@ -429,33 +324,21 @@
     <t>pré-romantisme</t>
   </si>
   <si>
-    <t>hogarth_1732.jpg</t>
-  </si>
-  <si>
     <t>Marriage A-la-Mode (I)</t>
   </si>
   <si>
-    <t>hogarth_1743.jpg</t>
-  </si>
-  <si>
     <t>Portrait présumé de Marie-Louise O'Murphy</t>
   </si>
   <si>
     <t>François Boucher</t>
   </si>
   <si>
-    <t>boucher_1752.jpg</t>
-  </si>
-  <si>
     <t>Arche en ruine</t>
   </si>
   <si>
     <t>Francesco Guardi</t>
   </si>
   <si>
-    <t>guardi_1760.jpg</t>
-  </si>
-  <si>
     <t>Piété Filiale</t>
   </si>
   <si>
@@ -465,30 +348,18 @@
     <t>morale</t>
   </si>
   <si>
-    <t>greuze_1763.jpg</t>
-  </si>
-  <si>
     <t>Les Hasards heureux de l'escarpolette</t>
   </si>
   <si>
     <t>Jean-Honoré Fragonard</t>
   </si>
   <si>
-    <t>fragonard_1767.jpg</t>
-  </si>
-  <si>
     <t>L'Ile de l'Amour</t>
   </si>
   <si>
-    <t>fragonard_1770.jpg</t>
-  </si>
-  <si>
     <t>Le grand prêtre Corésus se sacrifie pour sauver Callirhoé</t>
   </si>
   <si>
-    <t>fragonard_1765.jpg</t>
-  </si>
-  <si>
     <t>Marine avec naufrage</t>
   </si>
   <si>
@@ -498,97 +369,58 @@
     <t>romantisme</t>
   </si>
   <si>
-    <t>loutherbourg_1769.jpg</t>
-  </si>
-  <si>
     <t>The Defeat of the Spanish Armada</t>
   </si>
   <si>
-    <t>loutherbourg_1796.jpg</t>
-  </si>
-  <si>
     <t>Coalbrookdale de nuit</t>
   </si>
   <si>
-    <t>loutherbourg_1801.jpg</t>
-  </si>
-  <si>
     <t>L'Incendie de l'Hôtel-Dieu</t>
   </si>
   <si>
     <t>Jean-Baptiste-François Génillion</t>
   </si>
   <si>
-    <t>genillion_1772.jpg</t>
-  </si>
-  <si>
     <t>Bélisaire demandant l’aumône</t>
   </si>
   <si>
-    <t>david_1780.jpg</t>
-  </si>
-  <si>
     <t>La Douleur d'Andromaque</t>
   </si>
   <si>
-    <t>david_1783.jpg</t>
-  </si>
-  <si>
     <t>Le Serment des Horaces</t>
   </si>
   <si>
-    <t>david_1784.jpg</t>
-  </si>
-  <si>
     <t>Le Cauchemar</t>
   </si>
   <si>
     <t>Johann Heinrich Füssli</t>
   </si>
   <si>
-    <t>fussli_1781.jpg</t>
-  </si>
-  <si>
     <t>Démolition de l'église Saint-Jean-en-Grève</t>
   </si>
   <si>
     <t>Hubert Robert</t>
   </si>
   <si>
-    <t>robert_1800.jpg</t>
-  </si>
-  <si>
     <t>Le Sacre de Napoléon</t>
   </si>
   <si>
-    <t>david_1807.jpg</t>
-  </si>
-  <si>
     <t>Le Radeau de la Méduse</t>
   </si>
   <si>
     <t>Théodore Géricault</t>
   </si>
   <si>
-    <t>gericault_1818.jpg</t>
-  </si>
-  <si>
     <t>La Liberté guidant le peuple</t>
   </si>
   <si>
     <t>Eugène Delacroix</t>
   </si>
   <si>
-    <t>delacroix_1830.jpg</t>
-  </si>
-  <si>
     <t>Louise de Broglie</t>
   </si>
   <si>
     <t>Jean-Auguste-Dominique Ingres</t>
-  </si>
-  <si>
-    <t>ingres_1845.jpg</t>
   </si>
   <si>
     <t>Bonjour Monsieur Courbet</t>
@@ -606,19 +438,10 @@
 </t>
   </si>
   <si>
-    <t>courbet_1854.jpg</t>
-  </si>
-  <si>
     <t>Autoportrait au chien noir</t>
   </si>
   <si>
-    <t>courbet_1844.jpg</t>
-  </si>
-  <si>
     <t>Le Désespéré</t>
-  </si>
-  <si>
-    <t>courbet_1845.jpg</t>
   </si>
   <si>
     <t>Des glaneuses</t>
@@ -634,18 +457,12 @@
 </t>
   </si>
   <si>
-    <t>millet_1857.jpg</t>
-  </si>
-  <si>
     <t>Les Remords</t>
   </si>
   <si>
     <t>William Bouguereau</t>
   </si>
   <si>
-    <t>bouguereau_1862.jpg</t>
-  </si>
-  <si>
     <t>Le Déjeuner sur l'herbe</t>
   </si>
   <si>
@@ -655,75 +472,48 @@
     <t>réalisme</t>
   </si>
   <si>
-    <t>manet_1863.jpg</t>
-  </si>
-  <si>
     <t>L'Exécution de Maximilien</t>
   </si>
   <si>
-    <t>manet_1868.jpg</t>
-  </si>
-  <si>
     <t>Pollice verso</t>
   </si>
   <si>
     <t>Jean-Léon Gérôme</t>
   </si>
   <si>
-    <t>gerome_1872.jpg</t>
-  </si>
-  <si>
     <t>Impression soleil Levant</t>
   </si>
   <si>
-    <t>monet_1872.jpg</t>
-  </si>
-  <si>
     <t>Raboteurs de parquet</t>
   </si>
   <si>
     <t>Gustave Caillebotte</t>
   </si>
   <si>
-    <t>caillebotte_1875.jpg</t>
-  </si>
-  <si>
     <t>Phèdre</t>
   </si>
   <si>
     <t>Alexandre Cabanel</t>
   </si>
   <si>
-    <t>cabanel_1880.jpg</t>
-  </si>
-  <si>
     <t>Les Énervés de Jumièges</t>
   </si>
   <si>
     <t>Évariste-Vital Luminais</t>
   </si>
   <si>
-    <t>luminais_1880.jpg</t>
-  </si>
-  <si>
     <t>Le Déjeuner des canotiers</t>
   </si>
   <si>
     <t>Auguste Renoir</t>
   </si>
   <si>
-    <t>renoir_1880.webp</t>
-  </si>
-  <si>
     <t>Le Rêve</t>
   </si>
   <si>
     <t>Édouard Detaille</t>
   </si>
   <si>
-    <t>detaille_1888.jpg</t>
-  </si>
-  <si>
     <t>Autoportrait à l'oreille bandée</t>
   </si>
   <si>
@@ -733,33 +523,21 @@
     <t>post-impressionnisme</t>
   </si>
   <si>
-    <t>vangogh_1889.jpg</t>
-  </si>
-  <si>
     <t>Paysage Tahitien</t>
   </si>
   <si>
     <t>Paul Gauguin</t>
   </si>
   <si>
-    <t>gauguin_1891.jpg</t>
-  </si>
-  <si>
     <t>Cathédrale de Rouen</t>
   </si>
   <si>
-    <t>monet_1892.jpeg</t>
-  </si>
-  <si>
     <t>The Brook</t>
   </si>
   <si>
     <t>Paul Cézanne</t>
   </si>
   <si>
-    <t>cezanne_1898.jpg</t>
-  </si>
-  <si>
     <t>Autoportrait</t>
   </si>
   <si>
@@ -769,33 +547,21 @@
     <t>fauvisme</t>
   </si>
   <si>
-    <t>matisse_1900.jpg</t>
-  </si>
-  <si>
     <t>Estaque</t>
   </si>
   <si>
     <t>André Derain</t>
   </si>
   <si>
-    <t>derain_1905.jpg</t>
-  </si>
-  <si>
     <t>La Raie Verte</t>
   </si>
   <si>
-    <t>matisse_1905.jpeg</t>
-  </si>
-  <si>
     <t>Restaurant de la Machine à Bougival</t>
   </si>
   <si>
     <t>Maurice de Vlaminck</t>
   </si>
   <si>
-    <t>vlaminck_1905.jpg</t>
-  </si>
-  <si>
     <t>Le Viaduc à l’Estaque</t>
   </si>
   <si>
@@ -805,48 +571,30 @@
     <t>fauvisme, cubisme</t>
   </si>
   <si>
-    <t>braque_1908.png</t>
-  </si>
-  <si>
     <t>Violon et chandelier</t>
   </si>
   <si>
-    <t>braque_1910.jpg</t>
-  </si>
-  <si>
     <t>Nus dans la forêt</t>
   </si>
   <si>
     <t>Fernand Léger</t>
   </si>
   <si>
-    <t>leger_1910.jpg</t>
-  </si>
-  <si>
     <t>La Noce</t>
   </si>
   <si>
-    <t>leger_1911.jpg</t>
-  </si>
-  <si>
     <t>Bouteille de rhum et journal</t>
   </si>
   <si>
     <t>Juan Gris</t>
   </si>
   <si>
-    <t>gris_1914.jpg</t>
-  </si>
-  <si>
     <t>Le Coquelicot</t>
   </si>
   <si>
     <t>Kees van Dongen</t>
   </si>
   <si>
-    <t>dongen_1919.webp</t>
-  </si>
-  <si>
     <t>Le baiser</t>
   </si>
   <si>
@@ -856,15 +604,9 @@
     <t>art-nouveau</t>
   </si>
   <si>
-    <t>klimt_1908.jpg</t>
-  </si>
-  <si>
     <t>La Nuit Etoilée</t>
   </si>
   <si>
-    <t>vangogh_1890.jpg</t>
-  </si>
-  <si>
     <t>Salomé dansant devant Hérode</t>
   </si>
   <si>
@@ -877,9 +619,6 @@
     <t>Représentation de l'épisode biblique de Salomé dansant devant Hérode.</t>
   </si>
   <si>
-    <t>moreau_1876.jpg</t>
-  </si>
-  <si>
     <t>Le Cri</t>
   </si>
   <si>
@@ -889,16 +628,10 @@
     <t>expressionnisme</t>
   </si>
   <si>
-    <t>munch_1893.jpg</t>
-  </si>
-  <si>
     <t>La Ronde de nuit</t>
   </si>
   <si>
     <t>Rembrandt van Rijn</t>
-  </si>
-  <si>
-    <t>rembrandt_1642.jpg</t>
   </si>
   <si>
     <t>La Jeune Fille à la perle</t>
@@ -916,9 +649,6 @@
 </t>
   </si>
   <si>
-    <t>vermeer_1665.jpg</t>
-  </si>
-  <si>
     <t>Lavender Mist</t>
   </si>
   <si>
@@ -933,61 +663,40 @@
 </t>
   </si>
   <si>
-    <t>pollock_1950.jpg</t>
-  </si>
-  <si>
     <t>Ultimate Painting</t>
   </si>
   <si>
     <t>Ad Reinhardt</t>
   </si>
   <si>
-    <t>reinhardt_1963.jpg</t>
-  </si>
-  <si>
     <t>Untitled (Black, Red over Black on Red)</t>
   </si>
   <si>
     <t>Mark Rothko</t>
   </si>
   <si>
-    <t>rothko_1964.jpg</t>
-  </si>
-  <si>
     <t>Transfiguration</t>
   </si>
   <si>
     <t>Adolph Gottlieb</t>
   </si>
   <si>
-    <t>gottlieb_1969.jpg</t>
-  </si>
-  <si>
     <t>1er Janvier</t>
   </si>
   <si>
     <t>Willem De Kooning</t>
   </si>
   <si>
-    <t>kooning_1956.webp</t>
-  </si>
-  <si>
     <t>Cubi XII</t>
   </si>
   <si>
     <t>David Smith</t>
   </si>
   <si>
-    <t>smith_1963.jpg</t>
-  </si>
-  <si>
     <t>Dawn’s Wedding Chapel II</t>
   </si>
   <si>
     <t>Louise Nevelson</t>
-  </si>
-  <si>
-    <t>nevelson_1959.jpg</t>
   </si>
   <si>
     <t>Trois Drapeaux</t>
@@ -1008,31 +717,19 @@
 </t>
   </si>
   <si>
-    <t>johns_1958.jpg</t>
-  </si>
-  <si>
     <t>Crying Girl</t>
   </si>
   <si>
     <t>Roy Lichtenstein</t>
   </si>
   <si>
-    <t>lichtenstein_1963.jpg</t>
-  </si>
-  <si>
     <t>Campbell's soup cans</t>
   </si>
   <si>
     <t>Andy Warhol</t>
   </si>
   <si>
-    <t>warhol_1962.jpg</t>
-  </si>
-  <si>
     <t>Brillo Boxes</t>
-  </si>
-  <si>
-    <t>warhol_1964.avif</t>
   </si>
   <si>
     <t>Great American Nude n.99</t>
@@ -1046,13 +743,7 @@
 </t>
   </si>
   <si>
-    <t>wesselmann_1968.jpg</t>
-  </si>
-  <si>
     <t>Diptyque Marilyn</t>
-  </si>
-  <si>
-    <t>warhol_1963.jpg</t>
   </si>
   <si>
     <t>I am Still Alive</t>
@@ -1067,9 +758,6 @@
     <t xml:space="preserve">On Kawara envoyait à des galeristes des télégrammes comportant les seuls
 mots "I am Still Alive".
 </t>
-  </si>
-  <si>
-    <t>kawara_1969.jpg</t>
   </si>
   <si>
     <t>Information Room</t>
@@ -1084,9 +772,6 @@
 </t>
   </si>
   <si>
-    <t>kosuth_1970.jpg</t>
-  </si>
-  <si>
     <t>Air-Conditioning Show</t>
   </si>
   <si>
@@ -1099,9 +784,6 @@
 </t>
   </si>
   <si>
-    <t>artandlanguage_1967.jpg</t>
-  </si>
-  <si>
     <t>Stacks</t>
   </si>
   <si>
@@ -1109,9 +791,6 @@
   </si>
   <si>
     <t>minimalisme</t>
-  </si>
-  <si>
-    <t>judd_1965.jpg</t>
   </si>
   <si>
     <t>144 carrés de plomb</t>
@@ -1126,36 +805,24 @@
 </t>
   </si>
   <si>
-    <t>andre_1969.jpg</t>
-  </si>
-  <si>
     <t>Structures</t>
   </si>
   <si>
     <t>Sol Lewitt</t>
   </si>
   <si>
-    <t>lewitt_1974.jpg</t>
-  </si>
-  <si>
     <t>Hearts are Trumps</t>
   </si>
   <si>
     <t>John Everett Millais</t>
   </si>
   <si>
-    <t>millais_1872.jpg</t>
-  </si>
-  <si>
     <t>Anthropometrie</t>
   </si>
   <si>
     <t>Yves Klein</t>
   </si>
   <si>
-    <t>klein_1960.jpg</t>
-  </si>
-  <si>
     <t>Le Violon d'Ingres</t>
   </si>
   <si>
@@ -1165,105 +832,69 @@
     <t>surrealisme</t>
   </si>
   <si>
-    <t>ray_1924.jpg</t>
-  </si>
-  <si>
     <t>Le Voyageur contemplant une mer de nuages</t>
   </si>
   <si>
     <t>Caspar David Friedrich</t>
   </si>
   <si>
-    <t>friedrich_1818.jpg</t>
-  </si>
-  <si>
     <t>La Chute des damnés</t>
   </si>
   <si>
     <t>Pierre Paul Rubens</t>
   </si>
   <si>
-    <t>rubens_1620.jpg</t>
-  </si>
-  <si>
     <t>Un bar aux Folies Bergère</t>
   </si>
   <si>
     <t>Edouard Manet</t>
   </si>
   <si>
-    <t>manet_1882.jpg</t>
-  </si>
-  <si>
     <t>Nu descendant un escalier (N°2)</t>
   </si>
   <si>
     <t>Marcel Duchamp</t>
   </si>
   <si>
-    <t>duchamp_1912.jpg</t>
-  </si>
-  <si>
     <t>L'Empire des lumières</t>
   </si>
   <si>
     <t>René Magritte</t>
   </si>
   <si>
-    <t>magritte_1964.webp</t>
-  </si>
-  <si>
     <t>L'Île des morts</t>
   </si>
   <si>
     <t>Arnold Bocklin</t>
   </si>
   <si>
-    <t>bocklin_1886.jpg</t>
-  </si>
-  <si>
     <t>Paradiso Canto</t>
   </si>
   <si>
     <t>Gustave Doré</t>
   </si>
   <si>
-    <t>dore_1866.jpg</t>
-  </si>
-  <si>
     <t>Agésandros</t>
   </si>
   <si>
     <t>Laocoon</t>
   </si>
   <si>
-    <t>laocoon_-40.jpg</t>
-  </si>
-  <si>
     <t>Hermès portant Dionysos enfant</t>
   </si>
   <si>
-    <t>unknown_-330.jpg</t>
-  </si>
-  <si>
     <t>Myron</t>
   </si>
   <si>
     <t>Le Discobole</t>
   </si>
   <si>
-    <t>myron_-450.jpg</t>
-  </si>
-  <si>
     <t>Achilles et Ajax jouant aux dés</t>
   </si>
   <si>
     <t>Exékias</t>
   </si>
   <si>
-    <t>exekias_-550.jpeg</t>
-  </si>
-  <si>
     <t>hellénistique, antiquité</t>
   </si>
   <si>
@@ -1276,9 +907,6 @@
     <t>Briton Rivière</t>
   </si>
   <si>
-    <t>riviere_1888.jpg</t>
-  </si>
-  <si>
     <t>Requiescat = prière pour le repos d'un defunt</t>
   </si>
   <si>
@@ -1297,18 +925,12 @@
     <t>La Promenade</t>
   </si>
   <si>
-    <t>monet_1875.jpg</t>
-  </si>
-  <si>
     <t>Doryphore</t>
   </si>
   <si>
     <t>Polyclète</t>
   </si>
   <si>
-    <t>polyclete_-450.jpg</t>
-  </si>
-  <si>
     <t>classique, antiquité</t>
   </si>
   <si>
@@ -1318,18 +940,12 @@
     <t>Phidias</t>
   </si>
   <si>
-    <t>phidias_-450.jpg</t>
-  </si>
-  <si>
     <t>Praxitèle</t>
   </si>
   <si>
     <t>Les Époux Arnolfini</t>
   </si>
   <si>
-    <t>eyck_1434.jpg</t>
-  </si>
-  <si>
     <t>Note le reflet dans le mirroir</t>
   </si>
   <si>
@@ -1342,27 +958,15 @@
     <t>Jan van Eyck</t>
   </si>
   <si>
-    <t>weyden_1435.jpg</t>
-  </si>
-  <si>
     <t>Le Jugement dernier</t>
   </si>
   <si>
-    <t>weyden_1452.jpg</t>
-  </si>
-  <si>
     <t>Hans Memling</t>
   </si>
   <si>
-    <t>memling_1473.jpg</t>
-  </si>
-  <si>
     <t>Scènes de la Passion du Christ</t>
   </si>
   <si>
-    <t>memling_1470.jpg</t>
-  </si>
-  <si>
     <t>Représente 23 vignettes de la Vie du Christ</t>
   </si>
   <si>
@@ -1372,9 +976,6 @@
     <t>Le Pérugin</t>
   </si>
   <si>
-    <t>perugin_1481.jpg</t>
-  </si>
-  <si>
     <t>Le Pérugin était le maitre de Raphaël</t>
   </si>
   <si>
@@ -1382,12 +983,6 @@
   </si>
   <si>
     <t>quattrocento, renaissance</t>
-  </si>
-  <si>
-    <t>michelange_1504.jpg</t>
-  </si>
-  <si>
-    <t>velazquez_1657.webp</t>
   </si>
   <si>
     <t>Les Ménines</t>
@@ -1406,12 +1001,6 @@
     <t>Judith décapitant Holopherne</t>
   </si>
   <si>
-    <t>gentileschi_1620.jpg</t>
-  </si>
-  <si>
-    <t>caravage_1602.jpg</t>
-  </si>
-  <si>
     <t>Une artiste de l'école caravagienne. Le Caravage avait déjà peint la scène. La comparaison des deux est assez criante sur le regard féminin qu'Artemisia porte.</t>
   </si>
   <si>
@@ -1424,34 +1013,442 @@
     <t>J.M.W. Turner</t>
   </si>
   <si>
-    <t>turner_1800.jpg</t>
-  </si>
-  <si>
     <t>Buttermere Lake</t>
   </si>
   <si>
-    <t>turner_1798.jpg</t>
-  </si>
-  <si>
     <t>Flatford Mill</t>
   </si>
   <si>
     <t>John Constable</t>
   </si>
   <si>
-    <t>constable_1811.jpg</t>
-  </si>
-  <si>
     <t>John Constable est considéré comme le précurseur de l'impressionnisme, même s'il appartient techniquement au romantisme.</t>
   </si>
   <si>
     <t>Étude de paysage marin avec nuage de pluie</t>
   </si>
   <si>
-    <t>constable_1827.jpg</t>
-  </si>
-  <si>
     <t>Décidémment, ce gars est précurseur.</t>
+  </si>
+  <si>
+    <t>Le Christ Pantocrator</t>
+  </si>
+  <si>
+    <t>Un Dimanche après-midi à l’île de la Grande Jatte</t>
+  </si>
+  <si>
+    <t>Georges Seurat</t>
+  </si>
+  <si>
+    <t>pointillisme</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775767085/bernini_1633_frjvbm.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768323/turner_1800_yyuwn1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768323/seurat_1886_awovne.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768323/smith_1963_nekxcy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768322/servandoni_1731_ua2mfe.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768322/saenredam_1644_fuikcs.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768322/rothko_1964_ziyfag.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768322/robert_1800_cjxfj1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768321/riviere_1888_qad1vv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768321/renoir_1880_etyxho.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768321/rembrandt_1642_ax0xha.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768321/reinhardt_1963_iz7alp.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768321/ray_1924_durwbe.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768321/raphael_1519_ogoem5.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768320/raphael_1518_dbjmoe.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768320/raphael_1509_fn8oap.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768320/poussin_1649_ryk92x.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768320/pollock_1950_de2q6m.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768319/picasso_1937_oiflni.avif</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768319/perugin_1481_rqhbz2.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768319/phidias_-450_cuyznw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768319/pantocrator_1261_cwetf5.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768318/myron_-450_kujwf1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768318/nevelson_1959_xjcrw0.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768318/moreau_1876_t0t8yn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768318/monet_1898_be0vbb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768317/monet_1872_vxpg7j.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768317/monet_1892_hmba0r.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768317/millais_1872_rqdewc.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768316/michelange_1504_ioicoo.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768316/memling_1473_fta6vy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768316/matisse_1905_e7o1ri.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768316/michelange_1512_xexqrz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768316/memling_1470_zhgllc.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768315/manet_1882_e964nl.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768316/matisse_1900_d6f7zg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768315/manet_1868_pcyr0p.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768315/manet_1863_ervmha.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768315/magritte_1964_vosjqc.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768315/luminais_1880_pj1koi.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768314/loutherbourg_1801_inlblv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768314/lichtenstein_1963_jpw3fv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768314/loutherbourg_1769_iecskv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768314/lewitt_1974_kacyrn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768313/leger_1911_qssmxb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768313/leger_1910_njn2cb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768313/lebrun_1686_lvlzxn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768313/laocoon_-40_yywfyf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768313/klimt_1908_fkkmgb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768312/kosuth_1970_wiylhm.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768312/kooning_1956_qdvzmj.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768312/klein_1960_yxbggg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768312/kawara_1969_ikqrom.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768312/judd_1965_g77ynb.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768311/hogarth_1743_md9jsq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768311/johns_1958_ww0wmd.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768311/ingres_1845_bej4y9.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768311/holbein_1538_jbnv8p.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768310/guardi_1760_hqdlud.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768310/hogarth_1732_j1ynsz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768310/hals_1633_jelsbd.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768310/gris_1914_sx1k5l.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768310/gottlieb_1969_e5rrt7.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768310/greuze_1763_owafna.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768310/giotto_1297_dabolc.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768309/gerome_1872_bhbzb1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768309/fragonard_1770_vyc2px.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768309/gauguin_1891_moomm9.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768309/gentileschi_1620_bxy5iw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768309/gericault_1818_b7tzln.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768309/genillion_1772_c5kpq8.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768308/fussli_1781_yqyrlt.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768308/friedrich_1818_n5dfui.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768308/fragonard_1767_mal1es.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768307/fragonard_1765_qnn7x0.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768307/eyck_1434_vr6hh7.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768307/duccio_1285_zjsgdx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768307/exekias_-550_b2smmq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768307/duchamp_1912_ndyzsy.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768307/dore_1866_dzbqj6.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768306/donatello_1415_idpeg0.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768306/dongen_1919_h1so20.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768306/detaille_1888_vivmbn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768306/derain_1905_laspto.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768305/delacroix_1830_nsyxt7.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768305/vangogh_1890_iaiqq4.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768305/david_1784_utenkf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768305/david_1783_x4alip.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768305/david_1780_gp2jrw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768305/courbet_1854_y3pdul.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768304/courbet_1844_okill1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768304/courbet_1845_fc0mdw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768305/da_vinci_1503_xm3xj5.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768304/chardin_1728_qw4yqq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768304/constable_1827_c7oajk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768304/constable_1811_c81jkl.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768303/cezanne_1898_mi1bbd.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768303/caravage_1603_wwxrin.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768303/caravage_1600_dtvlxs.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768302/boucher_1752_xlku7l.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768303/caillebotte_1875_reuhi0.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768303/brueghel_1568_eeuzdk.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768302/brueghel_1563_f9ph2s.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768303/cabanel_1880_pfwsyf.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768302/braque_1910_fjdybu.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768302/braque_1908_dutdb4.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768302/botticelli_1482_q5bjez.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768302/bocklin_1886_vlus2d.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768301/zurbaran_1633_cno8mv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768301/weyden_1452_szuvgc.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768301/watteau_1718_qn70wa.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768301/warhol_1964_svuggw.avif</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768301/weyden_1435_jhe9gu.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768301/wesselmann_1968_qqeuzz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768300/vangogh_1889_ufznhn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768300/warhol_1963_puv4rq.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768300/warhol_1962_ho7atz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768300/vermeer_1665_yuz5qv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768300/vlaminck_1905_wikwtn.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768299/velazquez_1657_rlkfp6.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768299/unknown_-330_mmgtfz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775768262/bernini_1652_scaled_lpahiw.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775767743/andre_1969_w24298.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775767743/artandlanguage_1967_enerop.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775769832/turner_1798_gyrol3.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775769919/caravage_1602_zjxaem.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770035/polyclete_-450_njfgs6.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770119/monet_1875_est2bm.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770187/rubens_1620_frfqpz.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770240/munch_1893_gsskix.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770306/bouguereau_1862_koyoka.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770353/millet_1857_cq2s68.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770461/david_1807_zzvucg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770567/loutherbourg_1796_g9cznx.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770618/gaulli_1670_jwgd00.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770764/david_1793_iatjcv.jpg</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -1887,16 +1884,16 @@
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>339</v>
       </c>
       <c r="G2" s="4"/>
     </row>
     <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="5">
         <v>1644</v>
@@ -1905,21 +1902,21 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3">
         <v>1509</v>
@@ -1928,19 +1925,19 @@
         <v>2.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>329</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5">
         <v>1793</v>
@@ -1949,19 +1946,19 @@
         <v>4.5</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>449</v>
       </c>
       <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3">
         <v>1937</v>
@@ -1970,2823 +1967,2820 @@
         <v>2.5</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="C7" s="3">
+        <v>1285</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5">
-        <v>1090</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="5">
+        <v>1297</v>
+      </c>
+      <c r="D8" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C9" s="3">
+        <v>1415</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3">
-        <v>1285</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1482</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1503</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>406</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1512</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1518</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>328</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1519</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1538</v>
+      </c>
+      <c r="D15" s="5">
         <v>1.5</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1297</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="E15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>371</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1568</v>
+      </c>
+      <c r="D16" s="3">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1415</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1456</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1482</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1503</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="C17" s="5">
+        <v>1563</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" t="s">
+        <v>416</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="3">
-        <v>1512</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1518</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1519</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1538</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1568</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C19" s="5">
-        <v>1563</v>
+        <v>1603</v>
       </c>
       <c r="D19" s="5">
         <v>3.5</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>411</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C20" s="3">
-        <v>1600</v>
+        <v>1633</v>
       </c>
       <c r="D20" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C21" s="5">
-        <v>1603</v>
+        <v>1652</v>
       </c>
       <c r="D21" s="5">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>435</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C22" s="3">
         <v>1633</v>
       </c>
       <c r="D22" s="3">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C23" s="5">
-        <v>1652</v>
+        <v>1633</v>
       </c>
       <c r="D23" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="C24" s="3">
-        <v>1633</v>
+        <v>1649</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="4"/>
+        <v>330</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C25" s="5">
-        <v>1633</v>
+        <v>1670</v>
       </c>
       <c r="D25" s="5">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" t="s">
+        <v>448</v>
+      </c>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1686</v>
+      </c>
+      <c r="D26" s="3">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" t="s">
-        <v>95</v>
-      </c>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="3">
-        <v>1649</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1.5</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>99</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C27" s="5">
-        <v>1670</v>
+        <v>1718</v>
       </c>
       <c r="D27" s="5">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>424</v>
       </c>
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C28" s="3">
-        <v>1686</v>
+        <v>1728</v>
       </c>
       <c r="D28" s="3">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>106</v>
+        <v>407</v>
       </c>
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C29" s="5">
-        <v>1718</v>
+        <v>1731</v>
       </c>
       <c r="D29" s="5">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="F29" t="s">
-        <v>110</v>
+        <v>318</v>
       </c>
       <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="C30" s="3">
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="D30" s="3">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>113</v>
+        <v>373</v>
       </c>
       <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="C31" s="5">
-        <v>1731</v>
+        <v>1743</v>
       </c>
       <c r="D31" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>117</v>
+        <v>368</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="C32" s="3">
-        <v>1732</v>
+        <v>1752</v>
       </c>
       <c r="D32" s="3">
         <v>1.5</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>121</v>
+        <v>413</v>
       </c>
       <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="C33" s="5">
-        <v>1743</v>
+        <v>1760</v>
       </c>
       <c r="D33" s="5">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>123</v>
+        <v>372</v>
       </c>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C34" s="3">
-        <v>1752</v>
+        <v>1763</v>
       </c>
       <c r="D34" s="3">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>126</v>
+        <v>377</v>
       </c>
       <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="C35" s="5">
-        <v>1760</v>
+        <v>1767</v>
       </c>
       <c r="D35" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>387</v>
       </c>
       <c r="G35" s="6"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="C36" s="3">
-        <v>1763</v>
+        <v>1770</v>
       </c>
       <c r="D36" s="3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>133</v>
+        <v>380</v>
       </c>
       <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="C37" s="5">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="D37" s="5">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="F37" t="s">
-        <v>136</v>
+        <v>388</v>
       </c>
       <c r="G37" s="6"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C38" s="3">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="D38" s="3">
         <v>3</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>138</v>
+        <v>356</v>
       </c>
       <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C39" s="5">
-        <v>1765</v>
+        <v>1796</v>
       </c>
       <c r="D39" s="5">
         <v>3.5</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
-        <v>140</v>
+        <v>447</v>
       </c>
       <c r="G39" s="6"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="C40" s="3">
-        <v>1769</v>
+        <v>1801</v>
       </c>
       <c r="D40" s="3">
         <v>3</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>144</v>
+        <v>354</v>
       </c>
       <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="C41" s="5">
-        <v>1796</v>
+        <v>1772</v>
       </c>
       <c r="D41" s="5">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>146</v>
+        <v>384</v>
       </c>
       <c r="G41" s="6"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="C42" s="3">
-        <v>1801</v>
+        <v>1780</v>
       </c>
       <c r="D42" s="3">
         <v>3</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>148</v>
+        <v>402</v>
       </c>
       <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="B43" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="C43" s="5">
-        <v>1772</v>
+        <v>1783</v>
       </c>
       <c r="D43" s="5">
         <v>3</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>151</v>
+        <v>401</v>
       </c>
       <c r="G43" s="6"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C44" s="3">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="D44" s="3">
         <v>3</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>153</v>
+        <v>400</v>
       </c>
       <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="C45" s="5">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="D45" s="5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>155</v>
+        <v>385</v>
       </c>
       <c r="G45" s="6"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="C46" s="3">
-        <v>1784</v>
+        <v>1800</v>
       </c>
       <c r="D46" s="3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="C47" s="5">
-        <v>1781</v>
+        <v>1807</v>
       </c>
       <c r="D47" s="5">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>160</v>
+        <v>446</v>
       </c>
       <c r="G47" s="6"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="C48" s="3">
-        <v>1800</v>
+        <v>1818</v>
       </c>
       <c r="D48" s="3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>163</v>
+        <v>383</v>
       </c>
       <c r="G48" s="4"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="C49" s="5">
-        <v>1807</v>
+        <v>1830</v>
       </c>
       <c r="D49" s="5">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="F49" t="s">
-        <v>165</v>
+        <v>398</v>
       </c>
       <c r="G49" s="6"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="C50" s="3">
-        <v>1818</v>
+        <v>1845</v>
       </c>
       <c r="D50" s="3">
         <v>3</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>168</v>
+        <v>370</v>
       </c>
       <c r="G50" s="4"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="B51" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="C51" s="5">
-        <v>1830</v>
+        <v>1854</v>
       </c>
       <c r="D51" s="5">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F51" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="6"/>
+        <v>403</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="C52" s="3">
+        <v>1844</v>
+      </c>
+      <c r="D52" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="5">
         <v>1845</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D53" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F53" t="s">
+        <v>405</v>
+      </c>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1857</v>
+      </c>
+      <c r="D54" s="3">
         <v>3</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G52" s="4"/>
-    </row>
-    <row r="53" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>175</v>
-      </c>
-      <c r="B53" t="s">
-        <v>176</v>
-      </c>
-      <c r="C53" s="5">
-        <v>1854</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F53" t="s">
-        <v>178</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C54" s="3">
-        <v>1844</v>
-      </c>
-      <c r="D54" s="3">
-        <v>3.5</v>
-      </c>
       <c r="E54" s="4" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G54" s="4"/>
+        <v>445</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="C55" s="5">
-        <v>1845</v>
+        <v>1862</v>
       </c>
       <c r="D55" s="5">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="F55" t="s">
-        <v>182</v>
+        <v>444</v>
       </c>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="C56" s="3">
-        <v>1857</v>
+        <v>1863</v>
       </c>
       <c r="D56" s="3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>185</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G56" s="4"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="C57" s="5">
-        <v>1862</v>
+        <v>1868</v>
       </c>
       <c r="D57" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>394</v>
+        <v>132</v>
       </c>
       <c r="F57" t="s">
-        <v>189</v>
+        <v>350</v>
       </c>
       <c r="G57" s="6"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="C58" s="3">
-        <v>1863</v>
+        <v>1872</v>
       </c>
       <c r="D58" s="3">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>193</v>
+        <v>379</v>
       </c>
       <c r="G58" s="4"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="B59" t="s">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="C59" s="5">
-        <v>1868</v>
+        <v>1872</v>
       </c>
       <c r="D59" s="5">
         <v>3</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>192</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="G59" s="6"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="C60" s="3">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="D60" s="3">
         <v>3</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>394</v>
+        <v>132</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>198</v>
+        <v>414</v>
       </c>
       <c r="G60" s="4"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="C61" s="5">
-        <v>1872</v>
+        <v>1880</v>
       </c>
       <c r="D61" s="5">
         <v>3</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="F61" t="s">
-        <v>200</v>
+        <v>417</v>
       </c>
       <c r="G61" s="6"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>201</v>
+        <v>141</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="C62" s="3">
-        <v>1875</v>
+        <v>1880</v>
       </c>
       <c r="D62" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>192</v>
+        <v>271</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>203</v>
+        <v>353</v>
       </c>
       <c r="G62" s="4"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="B63" t="s">
-        <v>205</v>
+        <v>144</v>
       </c>
       <c r="C63" s="5">
         <v>1880</v>
       </c>
       <c r="D63" s="5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>395</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>206</v>
+        <v>323</v>
       </c>
       <c r="G63" s="6"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="C64" s="3">
-        <v>1880</v>
+        <v>1888</v>
       </c>
       <c r="D64" s="3">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>394</v>
+        <v>9</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>209</v>
+        <v>396</v>
       </c>
       <c r="G64" s="4"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>148</v>
       </c>
       <c r="C65" s="5">
-        <v>1880</v>
+        <v>1889</v>
       </c>
       <c r="D65" s="5">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="F65" t="s">
-        <v>212</v>
+        <v>428</v>
       </c>
       <c r="G65" s="6"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="C66" s="3">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="D66" s="3">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>215</v>
+        <v>381</v>
       </c>
       <c r="G66" s="4"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="B67" t="s">
-        <v>217</v>
+        <v>8</v>
       </c>
       <c r="C67" s="5">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="D67" s="5">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>218</v>
+        <v>9</v>
       </c>
       <c r="F67" t="s">
-        <v>219</v>
+        <v>341</v>
       </c>
       <c r="G67" s="6"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>221</v>
+        <v>154</v>
       </c>
       <c r="C68" s="3">
-        <v>1891</v>
+        <v>1898</v>
       </c>
       <c r="D68" s="3">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>218</v>
+        <v>9</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>222</v>
+        <v>410</v>
       </c>
       <c r="G68" s="4"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>155</v>
       </c>
       <c r="B69" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="C69" s="5">
-        <v>1892</v>
+        <v>1900</v>
       </c>
       <c r="D69" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>9</v>
+        <v>157</v>
       </c>
       <c r="F69" t="s">
-        <v>224</v>
+        <v>349</v>
       </c>
       <c r="G69" s="6"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>225</v>
+        <v>158</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>226</v>
+        <v>159</v>
       </c>
       <c r="C70" s="3">
-        <v>1898</v>
+        <v>1905</v>
       </c>
       <c r="D70" s="3">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>9</v>
+        <v>157</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>227</v>
+        <v>397</v>
       </c>
       <c r="G70" s="4"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>228</v>
+        <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="C71" s="5">
-        <v>1900</v>
+        <v>1905</v>
       </c>
       <c r="D71" s="5">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="F71" t="s">
-        <v>231</v>
+        <v>345</v>
       </c>
       <c r="G71" s="6"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="C72" s="3">
         <v>1905</v>
       </c>
       <c r="D72" s="3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>234</v>
+        <v>432</v>
       </c>
       <c r="G72" s="4"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>235</v>
+        <v>163</v>
       </c>
       <c r="B73" t="s">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="C73" s="5">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="D73" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="F73" t="s">
-        <v>236</v>
+        <v>419</v>
       </c>
       <c r="G73" s="6"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="C74" s="3">
-        <v>1905</v>
+        <v>1910</v>
       </c>
       <c r="D74" s="3">
         <v>3</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>239</v>
+        <v>418</v>
       </c>
       <c r="G74" s="4"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>240</v>
+        <v>167</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="C75" s="5">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="D75" s="5">
         <v>3</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>242</v>
+        <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>243</v>
+        <v>359</v>
       </c>
       <c r="G75" s="6"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="C76" s="3">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="D76" s="3">
         <v>3</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>245</v>
+        <v>358</v>
       </c>
       <c r="G76" s="4"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="B77" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
       <c r="C77" s="5">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="D77" s="5">
         <v>3</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>248</v>
+        <v>375</v>
       </c>
       <c r="G77" s="6"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>249</v>
+        <v>172</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="C78" s="3">
-        <v>1911</v>
+        <v>1919</v>
       </c>
       <c r="D78" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>26</v>
+        <v>157</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="G78" s="4"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>252</v>
+        <v>175</v>
       </c>
       <c r="C79" s="5">
-        <v>1914</v>
+        <v>1908</v>
       </c>
       <c r="D79" s="5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
       <c r="F79" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="G79" s="6"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>255</v>
+        <v>148</v>
       </c>
       <c r="C80" s="3">
-        <v>1919</v>
+        <v>1889</v>
       </c>
       <c r="D80" s="3">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>230</v>
+        <v>149</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>256</v>
+        <v>399</v>
       </c>
       <c r="G80" s="4"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>257</v>
+        <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>258</v>
+        <v>179</v>
       </c>
       <c r="C81" s="5">
-        <v>1908</v>
+        <v>1876</v>
       </c>
       <c r="D81" s="5">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="F81" t="s">
-        <v>260</v>
-      </c>
-      <c r="G81" s="6"/>
+        <v>338</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>261</v>
+        <v>182</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="C82" s="3">
-        <v>1889</v>
+        <v>1893</v>
       </c>
       <c r="D82" s="3">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>262</v>
+        <v>443</v>
       </c>
       <c r="G82" s="4"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c r="B83" t="s">
-        <v>264</v>
+        <v>186</v>
       </c>
       <c r="C83" s="5">
-        <v>1876</v>
+        <v>1642</v>
       </c>
       <c r="D83" s="5">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>265</v>
+        <v>57</v>
       </c>
       <c r="F83" t="s">
-        <v>267</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>268</v>
+        <v>187</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>269</v>
+        <v>188</v>
       </c>
       <c r="C84" s="3">
-        <v>1893</v>
+        <v>1665</v>
       </c>
       <c r="D84" s="3">
         <v>2.5</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>270</v>
+        <v>57</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G84" s="4"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>272</v>
+        <v>190</v>
       </c>
       <c r="B85" t="s">
-        <v>273</v>
+        <v>191</v>
       </c>
       <c r="C85" s="5">
-        <v>1642</v>
+        <v>1950</v>
       </c>
       <c r="D85" s="5">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="F85" t="s">
-        <v>274</v>
-      </c>
-      <c r="G85" s="6"/>
-    </row>
-    <row r="86" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>275</v>
+        <v>194</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>276</v>
+        <v>195</v>
       </c>
       <c r="C86" s="3">
-        <v>1665</v>
+        <v>1963</v>
       </c>
       <c r="D86" s="3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="B87" t="s">
-        <v>280</v>
+        <v>197</v>
       </c>
       <c r="C87" s="5">
-        <v>1950</v>
+        <v>1964</v>
       </c>
       <c r="D87" s="5">
         <v>3</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="F87" t="s">
-        <v>283</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>282</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="G87" s="6"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="C88" s="3">
-        <v>1963</v>
+        <v>1969</v>
       </c>
       <c r="D88" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>286</v>
+        <v>376</v>
       </c>
       <c r="G88" s="4"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>287</v>
+        <v>200</v>
       </c>
       <c r="B89" t="s">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="C89" s="5">
-        <v>1964</v>
+        <v>1956</v>
       </c>
       <c r="D89" s="5">
         <v>3</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="F89" t="s">
-        <v>289</v>
+        <v>364</v>
       </c>
       <c r="G89" s="6"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>290</v>
+        <v>202</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>291</v>
+        <v>203</v>
       </c>
       <c r="C90" s="3">
-        <v>1969</v>
+        <v>1963</v>
       </c>
       <c r="D90" s="3">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="G90" s="4"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>293</v>
+        <v>204</v>
       </c>
       <c r="B91" t="s">
-        <v>294</v>
+        <v>205</v>
       </c>
       <c r="C91" s="5">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="D91" s="5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>281</v>
+        <v>192</v>
       </c>
       <c r="F91" t="s">
-        <v>295</v>
+        <v>337</v>
       </c>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>296</v>
+        <v>206</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>297</v>
+        <v>207</v>
       </c>
       <c r="C92" s="3">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="D92" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>281</v>
+        <v>208</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G92" s="4"/>
+        <v>369</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>299</v>
+        <v>210</v>
       </c>
       <c r="B93" t="s">
-        <v>300</v>
+        <v>211</v>
       </c>
       <c r="C93" s="5">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="D93" s="5">
         <v>2.5</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>281</v>
+        <v>208</v>
       </c>
       <c r="F93" t="s">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="G93" s="6"/>
     </row>
-    <row r="94" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>302</v>
+        <v>212</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>303</v>
+        <v>213</v>
       </c>
       <c r="C94" s="3">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="D94" s="3">
         <v>1.5</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>304</v>
+        <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>305</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="G94" s="4"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>307</v>
+        <v>214</v>
       </c>
       <c r="B95" t="s">
-        <v>308</v>
+        <v>213</v>
       </c>
       <c r="C95" s="5">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D95" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F95" t="s">
+        <v>425</v>
+      </c>
+      <c r="G95" s="6"/>
+    </row>
+    <row r="96" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1968</v>
+      </c>
+      <c r="D96" s="3">
         <v>2.5</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="F95" t="s">
-        <v>309</v>
-      </c>
-      <c r="G95" s="6"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C96" s="3">
-        <v>1962</v>
-      </c>
-      <c r="D96" s="3">
-        <v>1.5</v>
-      </c>
       <c r="E96" s="4" t="s">
-        <v>304</v>
+        <v>208</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G96" s="4"/>
+        <v>427</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>313</v>
+        <v>218</v>
       </c>
       <c r="B97" t="s">
-        <v>311</v>
+        <v>213</v>
       </c>
       <c r="C97" s="5">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="D97" s="5">
         <v>1.5</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>304</v>
+        <v>208</v>
       </c>
       <c r="F97" t="s">
-        <v>314</v>
+        <v>429</v>
       </c>
       <c r="G97" s="6"/>
     </row>
     <row r="98" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>315</v>
+        <v>219</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>316</v>
+        <v>220</v>
       </c>
       <c r="C98" s="3">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D98" s="3">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>304</v>
+        <v>221</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>319</v>
+        <v>223</v>
       </c>
       <c r="B99" t="s">
-        <v>311</v>
+        <v>224</v>
       </c>
       <c r="C99" s="5">
-        <v>1962</v>
+        <v>1970</v>
       </c>
       <c r="D99" s="5">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>304</v>
+        <v>221</v>
       </c>
       <c r="F99" t="s">
-        <v>320</v>
-      </c>
-      <c r="G99" s="6"/>
-    </row>
-    <row r="100" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>321</v>
+        <v>226</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>322</v>
+        <v>227</v>
       </c>
       <c r="C100" s="3">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="D100" s="3">
         <v>1</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>323</v>
+        <v>221</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="B101" t="s">
-        <v>327</v>
+        <v>230</v>
       </c>
       <c r="C101" s="5">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="D101" s="5">
         <v>2</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>323</v>
+        <v>231</v>
       </c>
       <c r="F101" t="s">
-        <v>329</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>328</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="G101" s="6"/>
     </row>
     <row r="102" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="C102" s="3">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="D102" s="3">
         <v>1</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>323</v>
+        <v>231</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>333</v>
+        <v>436</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>334</v>
+        <v>235</v>
       </c>
       <c r="B103" t="s">
-        <v>335</v>
+        <v>236</v>
       </c>
       <c r="C103" s="5">
-        <v>1965</v>
+        <v>1974</v>
       </c>
       <c r="D103" s="5">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>336</v>
+        <v>231</v>
       </c>
       <c r="F103" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="G103" s="6"/>
     </row>
-    <row r="104" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="C104" s="3">
-        <v>1969</v>
+        <v>1872</v>
       </c>
       <c r="D104" s="3">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>340</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="G104" s="4"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>342</v>
+        <v>239</v>
       </c>
       <c r="B105" t="s">
-        <v>343</v>
+        <v>240</v>
       </c>
       <c r="C105" s="5">
-        <v>1974</v>
+        <v>1960</v>
       </c>
       <c r="D105" s="5">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>336</v>
+        <v>192</v>
       </c>
       <c r="F105" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="G105" s="6"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>345</v>
+        <v>241</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>346</v>
+        <v>242</v>
       </c>
       <c r="C106" s="3">
-        <v>1872</v>
+        <v>1924</v>
       </c>
       <c r="D106" s="3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="G106" s="4"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>348</v>
+        <v>244</v>
       </c>
       <c r="B107" t="s">
-        <v>349</v>
+        <v>245</v>
       </c>
       <c r="C107" s="5">
-        <v>1960</v>
+        <v>1818</v>
       </c>
       <c r="D107" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>281</v>
+        <v>101</v>
       </c>
       <c r="F107" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="G107" s="6"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>351</v>
+        <v>246</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>352</v>
+        <v>247</v>
       </c>
       <c r="C108" s="3">
-        <v>1924</v>
+        <v>1620</v>
       </c>
       <c r="D108" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>353</v>
+        <v>57</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>354</v>
+        <v>442</v>
       </c>
       <c r="G108" s="4"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>355</v>
+        <v>248</v>
       </c>
       <c r="B109" t="s">
-        <v>356</v>
+        <v>249</v>
       </c>
       <c r="C109" s="5">
-        <v>1818</v>
+        <v>1882</v>
       </c>
       <c r="D109" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>143</v>
+        <v>273</v>
       </c>
       <c r="F109" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="G109" s="6"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>358</v>
+        <v>250</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>359</v>
+        <v>251</v>
       </c>
       <c r="C110" s="3">
-        <v>1620</v>
+        <v>1912</v>
       </c>
       <c r="D110" s="3">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="G110" s="4"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>361</v>
+        <v>252</v>
       </c>
       <c r="B111" t="s">
-        <v>362</v>
+        <v>253</v>
       </c>
       <c r="C111" s="5">
-        <v>1882</v>
+        <v>1964</v>
       </c>
       <c r="D111" s="5">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>396</v>
+        <v>243</v>
       </c>
       <c r="F111" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="G111" s="6"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>364</v>
+        <v>254</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>365</v>
+        <v>255</v>
       </c>
       <c r="C112" s="3">
-        <v>1912</v>
+        <v>1886</v>
       </c>
       <c r="D112" s="3">
         <v>3.5</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>366</v>
+        <v>421</v>
       </c>
       <c r="G112" s="4"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>367</v>
+        <v>256</v>
       </c>
       <c r="B113" t="s">
-        <v>368</v>
+        <v>257</v>
       </c>
       <c r="C113" s="5">
-        <v>1964</v>
+        <v>1866</v>
       </c>
       <c r="D113" s="5">
         <v>4.5</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>353</v>
+        <v>101</v>
       </c>
       <c r="F113" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="G113" s="6"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>370</v>
+        <v>258</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>371</v>
+        <v>259</v>
       </c>
       <c r="C114" s="3">
-        <v>1886</v>
+        <v>-40</v>
       </c>
       <c r="D114" s="3">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>265</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="G114" s="4"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>373</v>
+        <v>280</v>
       </c>
       <c r="B115" t="s">
-        <v>374</v>
+        <v>260</v>
       </c>
       <c r="C115" s="5">
-        <v>1866</v>
+        <v>-330</v>
       </c>
       <c r="D115" s="5">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="F115" t="s">
-        <v>375</v>
-      </c>
-      <c r="G115" s="6"/>
+        <v>434</v>
+      </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>376</v>
+        <v>261</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>377</v>
+        <v>262</v>
       </c>
       <c r="C116" s="3">
-        <v>-40</v>
+        <v>-450</v>
       </c>
       <c r="D116" s="3">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>387</v>
+        <v>277</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>378</v>
+        <v>336</v>
       </c>
       <c r="G116" s="4"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>406</v>
+        <v>264</v>
       </c>
       <c r="B117" t="s">
-        <v>379</v>
+        <v>263</v>
       </c>
       <c r="C117" s="5">
-        <v>-330</v>
+        <v>-550</v>
       </c>
       <c r="D117" s="5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>387</v>
+        <v>266</v>
       </c>
       <c r="F117" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>381</v>
+        <v>267</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>382</v>
+        <v>268</v>
       </c>
       <c r="C118" s="3">
-        <v>-450</v>
+        <v>1888</v>
       </c>
       <c r="D118" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>402</v>
+        <v>270</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="G118" s="4"/>
+        <v>322</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>385</v>
+        <v>274</v>
       </c>
       <c r="B119" t="s">
-        <v>384</v>
+        <v>8</v>
       </c>
       <c r="C119" s="5">
-        <v>-550</v>
+        <v>1875</v>
       </c>
       <c r="D119" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>388</v>
+        <v>9</v>
       </c>
       <c r="F119" t="s">
-        <v>386</v>
+        <v>441</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>389</v>
+        <v>275</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>390</v>
+        <v>276</v>
       </c>
       <c r="C120" s="3">
-        <v>1888</v>
+        <v>-450</v>
       </c>
       <c r="D120" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>393</v>
+        <v>277</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>392</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="G120" s="4"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>397</v>
+        <v>278</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>279</v>
       </c>
       <c r="C121" s="5">
-        <v>1875</v>
+        <v>-450</v>
       </c>
       <c r="D121" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>9</v>
+        <v>277</v>
       </c>
       <c r="F121" t="s">
-        <v>398</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>399</v>
+        <v>281</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>400</v>
+        <v>285</v>
       </c>
       <c r="C122" s="3">
-        <v>-450</v>
+        <v>1434</v>
       </c>
       <c r="D122" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>402</v>
+        <v>48</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G122" s="4"/>
+        <v>389</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>403</v>
+        <v>283</v>
       </c>
       <c r="B123" t="s">
-        <v>404</v>
+        <v>284</v>
       </c>
       <c r="C123" s="5">
-        <v>-450</v>
+        <v>1435</v>
       </c>
       <c r="D123" s="5">
         <v>1</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>402</v>
+        <v>48</v>
       </c>
       <c r="F123" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>407</v>
+        <v>286</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>412</v>
+        <v>284</v>
       </c>
       <c r="C124" s="3">
-        <v>1434</v>
+        <v>1452</v>
       </c>
       <c r="D124" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>409</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="G124" s="4"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>410</v>
+        <v>286</v>
       </c>
       <c r="B125" t="s">
-        <v>411</v>
+        <v>287</v>
       </c>
       <c r="C125" s="5">
-        <v>1435</v>
+        <v>1473</v>
       </c>
       <c r="D125" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="F125" t="s">
-        <v>413</v>
+        <v>344</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>414</v>
+        <v>288</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>411</v>
+        <v>287</v>
       </c>
       <c r="C126" s="3">
-        <v>1452</v>
+        <v>1470</v>
       </c>
       <c r="D126" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="G126" s="4"/>
+        <v>347</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>414</v>
+        <v>290</v>
       </c>
       <c r="B127" t="s">
-        <v>416</v>
+        <v>291</v>
       </c>
       <c r="C127" s="5">
-        <v>1473</v>
+        <v>1481</v>
       </c>
       <c r="D127" s="5">
         <v>2</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>67</v>
+        <v>294</v>
       </c>
       <c r="F127" t="s">
-        <v>417</v>
+        <v>333</v>
+      </c>
+      <c r="G127" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>418</v>
+        <v>293</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>416</v>
+        <v>41</v>
       </c>
       <c r="C128" s="3">
-        <v>1470</v>
+        <v>1504</v>
       </c>
       <c r="D128" s="3">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="G128" s="4"/>
+    </row>
+    <row r="129" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>421</v>
+        <v>295</v>
       </c>
       <c r="B129" t="s">
-        <v>422</v>
+        <v>296</v>
       </c>
       <c r="C129" s="5">
-        <v>1481</v>
+        <v>1657</v>
       </c>
       <c r="D129" s="5">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>426</v>
+        <v>57</v>
       </c>
       <c r="F129" t="s">
-        <v>423</v>
-      </c>
-      <c r="G129" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="G129" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>425</v>
+        <v>299</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C130" s="3">
+        <v>1620</v>
+      </c>
+      <c r="D130" s="3">
+        <v>3</v>
+      </c>
+      <c r="E130" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C130" s="3">
-        <v>1504</v>
-      </c>
-      <c r="D130" s="3">
-        <v>4</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="F130" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="G130" s="4"/>
-    </row>
-    <row r="131" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>429</v>
+        <v>299</v>
       </c>
       <c r="B131" t="s">
-        <v>430</v>
+        <v>56</v>
       </c>
       <c r="C131" s="5">
-        <v>1657</v>
+        <v>1602</v>
       </c>
       <c r="D131" s="5">
         <v>2.5</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F131" t="s">
-        <v>428</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+      <c r="G131" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>433</v>
+        <v>302</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>432</v>
+        <v>303</v>
       </c>
       <c r="C132" s="3">
-        <v>1620</v>
+        <v>1800</v>
       </c>
       <c r="D132" s="3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>436</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="G132" s="4"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>433</v>
+        <v>304</v>
       </c>
       <c r="B133" t="s">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="C133" s="5">
-        <v>1602</v>
+        <v>1798</v>
       </c>
       <c r="D133" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F133" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C134" s="3">
+        <v>1811</v>
+      </c>
+      <c r="D134" s="3">
         <v>2.5</v>
       </c>
-      <c r="E133" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F133" t="s">
-        <v>435</v>
-      </c>
-      <c r="G133" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C134" s="3">
-        <v>1800</v>
-      </c>
-      <c r="D134" s="3">
-        <v>3.5</v>
-      </c>
       <c r="E134" s="4" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="G134" s="4"/>
+        <v>409</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>441</v>
+        <v>308</v>
       </c>
       <c r="B135" t="s">
-        <v>439</v>
+        <v>306</v>
       </c>
       <c r="C135" s="5">
-        <v>1798</v>
+        <v>1827</v>
       </c>
       <c r="D135" s="5">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="F135" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+      <c r="G135" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>443</v>
+        <v>310</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>444</v>
+        <v>23</v>
       </c>
       <c r="C136" s="3">
-        <v>1811</v>
+        <v>1261</v>
       </c>
       <c r="D136" s="3">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>446</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="G136" s="4"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>447</v>
+        <v>311</v>
       </c>
       <c r="B137" t="s">
-        <v>444</v>
+        <v>312</v>
       </c>
       <c r="C137" s="5">
-        <v>1827</v>
+        <v>1886</v>
       </c>
       <c r="D137" s="5">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>143</v>
+        <v>313</v>
       </c>
       <c r="F137" t="s">
-        <v>448</v>
-      </c>
-      <c r="G137" t="s">
-        <v>449</v>
+        <v>316</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -4870,15 +4864,6 @@
       <c r="F154" s="2"/>
       <c r="G154" s="4"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="2"/>
-      <c r="B156" s="2"/>
-      <c r="C156" s="3"/>
-      <c r="D156" s="3"/>
-      <c r="E156" s="4"/>
-      <c r="F156" s="2"/>
-      <c r="G156" s="4"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/artworks.xlsx
+++ b/public/artworks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\dev\artbook\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0200EEF1-89B6-420E-B6EA-B0AFCD0EAF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF492282-39E8-48E8-840D-D2B2BD1E09DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="551">
   <si>
     <t>title</t>
   </si>
@@ -1001,9 +1001,6 @@
     <t>Judith décapitant Holopherne</t>
   </si>
   <si>
-    <t>Une artiste de l'école caravagienne. Le Caravage avait déjà peint la scène. La comparaison des deux est assez criante sur le regard féminin qu'Artemisia porte.</t>
-  </si>
-  <si>
     <t>Artemisia Gentileschi a peint la même scène en 1620, avec un regard moins masculin.</t>
   </si>
   <si>
@@ -1449,6 +1446,313 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775770764/david_1793_iatjcv.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775841674/blake_1810_oyxds8.jpg</t>
+  </si>
+  <si>
+    <t>Grand Dragon Rouge</t>
+  </si>
+  <si>
+    <t>William Blake</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775841803/martin_1841_byybb4.jpg</t>
+  </si>
+  <si>
+    <t>Le Pandemonium</t>
+  </si>
+  <si>
+    <t>John Martin</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775842435/rubens_1614_mpxdvr.jpg</t>
+  </si>
+  <si>
+    <t>La Descente de Croix</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775904963/strazza_1860_oqqati.jpg</t>
+  </si>
+  <si>
+    <t>La Vierge voilée</t>
+  </si>
+  <si>
+    <t>Giovanni Strazza</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775905152/pissarro_1897_fbrbso.jpg</t>
+  </si>
+  <si>
+    <t>Boulevard Montmartre, matin d'hiver</t>
+  </si>
+  <si>
+    <t>Camille Pissarro</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775905274/claudel_1905_rx9ik4.jpg</t>
+  </si>
+  <si>
+    <t>La Valse</t>
+  </si>
+  <si>
+    <t>Camille Claudel</t>
+  </si>
+  <si>
+    <t>La Danaïde</t>
+  </si>
+  <si>
+    <t>Auguste Rodin</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775905453/rodin_1889_boomqp.jpg</t>
+  </si>
+  <si>
+    <t>Connue comme l'oeuvre qui a démarré l'impressionnisme.</t>
+  </si>
+  <si>
+    <t>Une artiste de l'école caravagienne. Le Caravage avait déjà peint la scène. La comparaison des deux est assez criante sur le regard féminin qu'Artemisia porte. Elle donne son visage à Judith, et celui de son violeur à Holopherne.</t>
+  </si>
+  <si>
+    <t>L'Homme en mouvement</t>
+  </si>
+  <si>
+    <t>Umberto Boccioni</t>
+  </si>
+  <si>
+    <t>futurisme</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775906549/boccioni_1913_je0wn5.jpg</t>
+  </si>
+  <si>
+    <t>Inspiré du cubisme ; Représente dynamiquement le mouvement vers l'avant, symbole du progrès.</t>
+  </si>
+  <si>
+    <t>Fontaine</t>
+  </si>
+  <si>
+    <t>dada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775907051/duchamp_1917_wecuse.jpg</t>
+  </si>
+  <si>
+    <t>Avec cette œuvre, Duchamp crée les ready-mades et questionne le rôle de la réalisation matérielle dans l'art, en plus de montrer le pouvoir des institutions, qui détiennent le pouvoir de décider si quelque chose est de l'art ou non.</t>
+  </si>
+  <si>
+    <t>Les Amants</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775908279/magritte_1928_o2yckz.png</t>
+  </si>
+  <si>
+    <t>Les Deux Fridas</t>
+  </si>
+  <si>
+    <t>Frida Kahlo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775909110/khalo_1939_uzsfh2.webp</t>
+  </si>
+  <si>
+    <t>Composition avec grand plan rouge, jaune, noir, gris et bleu</t>
+  </si>
+  <si>
+    <t>Piet Mondrian</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775909198/mondrian_1921_ycsuzj.webp</t>
+  </si>
+  <si>
+    <t>City Landscapes</t>
+  </si>
+  <si>
+    <t>Jeremy Mann</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775915393/mann_2016_h8t4e0.jpg</t>
+  </si>
+  <si>
+    <t>Alpay Efe</t>
+  </si>
+  <si>
+    <t>Flare</t>
+  </si>
+  <si>
+    <t>contemporary</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775915583/efe_2021_bi99mk.webp</t>
+  </si>
+  <si>
+    <t>Aykut Aydogdu</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775916387/aydogdu_2018_juf7bl.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775916547/aydogdu_2019_sxuhsh.jpg</t>
+  </si>
+  <si>
+    <t>Laura H. Rubin</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775916927/rubin_2024_i2tivt.avif</t>
+  </si>
+  <si>
+    <t>Cosmic Abstraction (N°2)</t>
+  </si>
+  <si>
+    <t>Victoria Topping</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775917099/topping_2020_v9u9tb.webp</t>
+  </si>
+  <si>
+    <t>Refik Anadol</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775917336/anadol_2022_yfesdp.jpg</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/CyQtuiTryoU/?amp%3Bigshid=MzRlODBiNWFlZA%3D%3D&amp;img_index=2</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>contemporary, generative</t>
+  </si>
+  <si>
+    <t>Erik Johansson</t>
+  </si>
+  <si>
+    <t>Full Moon Service</t>
+  </si>
+  <si>
+    <t>contemporary, surrealisme</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775918005/johansson_2016_ybidyp.webp</t>
+  </si>
+  <si>
+    <t>Behind the scenes : https://www.youtube.com/watch?v=6gHmKBym2pc</t>
+  </si>
+  <si>
+    <t>Composition VIII</t>
+  </si>
+  <si>
+    <t>Vassily Kandinsky</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775935307/kandinsky_1923_wdgeze.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775935370/kandinsky_1926_ljlqrg.jpg</t>
+  </si>
+  <si>
+    <t>Quelques Cercles</t>
+  </si>
+  <si>
+    <t>Gaea</t>
+  </si>
+  <si>
+    <t>Lee Krasner</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775935637/krasner_1966_evrxn6.jpg</t>
+  </si>
+  <si>
+    <t>Femme de Jackson Pollock, à qui globalement il aurait tout volé.</t>
+  </si>
+  <si>
+    <t>Untitled Film Still</t>
+  </si>
+  <si>
+    <t>Cindy Sherman</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775936320/1980_sherman_ozcfay.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette photo fait parti d'une série d'autres, qui questionnent par visibilisation la place de la femme dans la société, en particulier tout les trucs casse couille qu'elle doit faire.
+</t>
+  </si>
+  <si>
+    <t>Maman</t>
+  </si>
+  <si>
+    <t>Louise Bourgeois</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775936672/bourgeois_1999_tliqym.avif</t>
+  </si>
+  <si>
+    <t>Avec son titre, on pourrait penser qu'elle en veut à sa mère. Mais en fait non. Elle aime bien les araignées. Sa mère est morte quand elle était jeune, et elle voit dans l'araignée une figure protectrice et forte.</t>
+  </si>
+  <si>
+    <t>Seascape</t>
+  </si>
+  <si>
+    <t>Gerhard Richter</t>
+  </si>
+  <si>
+    <t>inconnu</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775936928/richter_1968_nz2d47.png</t>
+  </si>
+  <si>
+    <t>Lake George Reflection</t>
+  </si>
+  <si>
+    <t>Georgia O'Keeffe</t>
+  </si>
+  <si>
+    <t>modernisme</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775937181/okeeffe_1923_aglrgw.jpg</t>
+  </si>
+  <si>
+    <t>Propped</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1775937830/saville_1992_hu2elf.avif</t>
+  </si>
+  <si>
+    <t>Jenny Saville</t>
+  </si>
+  <si>
+    <t>Le Moine au bord de la mer</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1776000539/friedrich_1810_ejsnyw.jpg</t>
+  </si>
+  <si>
+    <t>Madame X</t>
+  </si>
+  <si>
+    <t>John Singer Sargent</t>
+  </si>
+  <si>
+    <t>Nonchaloir</t>
+  </si>
+  <si>
+    <t>Carnation, Lily, Lily, Rose</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1776001235/sargent_1911_fnbelg.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1776001323/sargent_1884_k1txf4.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dueqjmfkw/image/upload/v1776001237/sargent_1885_i61cth.jpg</t>
   </si>
 </sst>
 </file>
@@ -1832,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G309"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -1884,7 +2188,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -1905,7 +2209,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>13</v>
@@ -1928,7 +2232,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1949,7 +2253,7 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G5" s="6"/>
     </row>
@@ -1970,7 +2274,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -1991,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>27</v>
@@ -2014,7 +2318,7 @@
         <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G8" s="6"/>
     </row>
@@ -2035,7 +2339,7 @@
         <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -2056,7 +2360,7 @@
         <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>36</v>
@@ -2079,7 +2383,7 @@
         <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>39</v>
@@ -2102,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>42</v>
@@ -2125,7 +2429,7 @@
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>44</v>
@@ -2148,7 +2452,7 @@
         <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -2169,7 +2473,7 @@
         <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>49</v>
@@ -2192,7 +2496,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>52</v>
@@ -2215,7 +2519,7 @@
         <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>54</v>
@@ -2238,7 +2542,7 @@
         <v>57</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>58</v>
@@ -2261,7 +2565,7 @@
         <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>58</v>
@@ -2284,7 +2588,7 @@
         <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>62</v>
@@ -2307,7 +2611,7 @@
         <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>62</v>
@@ -2330,7 +2634,7 @@
         <v>57</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -2351,7 +2655,7 @@
         <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G23" s="6"/>
     </row>
@@ -2372,7 +2676,7 @@
         <v>70</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>71</v>
@@ -2395,7 +2699,7 @@
         <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G25" s="6"/>
     </row>
@@ -2416,7 +2720,7 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -2437,7 +2741,7 @@
         <v>78</v>
       </c>
       <c r="F27" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G27" s="6"/>
     </row>
@@ -2458,7 +2762,7 @@
         <v>78</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G28" s="4"/>
     </row>
@@ -2479,7 +2783,7 @@
         <v>83</v>
       </c>
       <c r="F29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G29" s="6"/>
     </row>
@@ -2500,7 +2804,7 @@
         <v>86</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G30" s="4"/>
     </row>
@@ -2521,7 +2825,7 @@
         <v>86</v>
       </c>
       <c r="F31" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G31" s="6"/>
     </row>
@@ -2542,7 +2846,7 @@
         <v>78</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G32" s="4"/>
     </row>
@@ -2563,7 +2867,7 @@
         <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G33" s="6"/>
     </row>
@@ -2584,7 +2888,7 @@
         <v>94</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G34" s="4"/>
     </row>
@@ -2605,7 +2909,7 @@
         <v>78</v>
       </c>
       <c r="F35" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G35" s="6"/>
     </row>
@@ -2626,7 +2930,7 @@
         <v>78</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G36" s="4"/>
     </row>
@@ -2647,7 +2951,7 @@
         <v>78</v>
       </c>
       <c r="F37" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G37" s="6"/>
     </row>
@@ -2668,7 +2972,7 @@
         <v>101</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G38" s="4"/>
     </row>
@@ -2689,7 +2993,7 @@
         <v>101</v>
       </c>
       <c r="F39" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G39" s="6"/>
     </row>
@@ -2710,7 +3014,7 @@
         <v>101</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G40" s="4"/>
     </row>
@@ -2731,7 +3035,7 @@
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G41" s="6"/>
     </row>
@@ -2752,7 +3056,7 @@
         <v>19</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G42" s="4"/>
     </row>
@@ -2773,7 +3077,7 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G43" s="6"/>
     </row>
@@ -2794,7 +3098,7 @@
         <v>19</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G44" s="4"/>
     </row>
@@ -2815,7 +3119,7 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G45" s="6"/>
     </row>
@@ -2836,7 +3140,7 @@
         <v>19</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G46" s="4"/>
     </row>
@@ -2857,7 +3161,7 @@
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G47" s="6"/>
     </row>
@@ -2878,7 +3182,7 @@
         <v>101</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G48" s="4"/>
     </row>
@@ -2899,7 +3203,7 @@
         <v>101</v>
       </c>
       <c r="F49" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G49" s="6"/>
     </row>
@@ -2920,7 +3224,7 @@
         <v>19</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G50" s="4"/>
     </row>
@@ -2941,7 +3245,7 @@
         <v>132</v>
       </c>
       <c r="F51" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>122</v>
@@ -2964,7 +3268,7 @@
         <v>132</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G52" s="4"/>
     </row>
@@ -2985,7 +3289,7 @@
         <v>132</v>
       </c>
       <c r="F53" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G53" s="6"/>
     </row>
@@ -3006,7 +3310,7 @@
         <v>132</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>127</v>
@@ -3029,7 +3333,7 @@
         <v>271</v>
       </c>
       <c r="F55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G55" s="6"/>
     </row>
@@ -3050,7 +3354,7 @@
         <v>132</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G56" s="4"/>
     </row>
@@ -3071,7 +3375,7 @@
         <v>132</v>
       </c>
       <c r="F57" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G57" s="6"/>
     </row>
@@ -3092,7 +3396,7 @@
         <v>271</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G58" s="4"/>
     </row>
@@ -3113,9 +3417,11 @@
         <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>340</v>
-      </c>
-      <c r="G59" s="6"/>
+        <v>339</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
@@ -3134,7 +3440,7 @@
         <v>132</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G60" s="4"/>
     </row>
@@ -3155,7 +3461,7 @@
         <v>272</v>
       </c>
       <c r="F61" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G61" s="6"/>
     </row>
@@ -3176,7 +3482,7 @@
         <v>271</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G62" s="4"/>
     </row>
@@ -3197,7 +3503,7 @@
         <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G63" s="6"/>
     </row>
@@ -3218,7 +3524,7 @@
         <v>9</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G64" s="4"/>
     </row>
@@ -3239,7 +3545,7 @@
         <v>149</v>
       </c>
       <c r="F65" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G65" s="6"/>
     </row>
@@ -3260,7 +3566,7 @@
         <v>149</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G66" s="4"/>
     </row>
@@ -3281,7 +3587,7 @@
         <v>9</v>
       </c>
       <c r="F67" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G67" s="6"/>
     </row>
@@ -3302,7 +3608,7 @@
         <v>9</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G68" s="4"/>
     </row>
@@ -3323,7 +3629,7 @@
         <v>157</v>
       </c>
       <c r="F69" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G69" s="6"/>
     </row>
@@ -3344,7 +3650,7 @@
         <v>157</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G70" s="4"/>
     </row>
@@ -3365,7 +3671,7 @@
         <v>157</v>
       </c>
       <c r="F71" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G71" s="6"/>
     </row>
@@ -3386,7 +3692,7 @@
         <v>157</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G72" s="4"/>
     </row>
@@ -3407,7 +3713,7 @@
         <v>165</v>
       </c>
       <c r="F73" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G73" s="6"/>
     </row>
@@ -3428,7 +3734,7 @@
         <v>22</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G74" s="4"/>
     </row>
@@ -3449,7 +3755,7 @@
         <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G75" s="6"/>
     </row>
@@ -3470,7 +3776,7 @@
         <v>22</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G76" s="4"/>
     </row>
@@ -3491,7 +3797,7 @@
         <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G77" s="6"/>
     </row>
@@ -3512,7 +3818,7 @@
         <v>157</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G78" s="4"/>
     </row>
@@ -3533,7 +3839,7 @@
         <v>176</v>
       </c>
       <c r="F79" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G79" s="6"/>
     </row>
@@ -3554,7 +3860,7 @@
         <v>149</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G80" s="4"/>
     </row>
@@ -3575,7 +3881,7 @@
         <v>180</v>
       </c>
       <c r="F81" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>181</v>
@@ -3598,7 +3904,7 @@
         <v>184</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G82" s="4"/>
     </row>
@@ -3619,7 +3925,7 @@
         <v>57</v>
       </c>
       <c r="F83" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G83" s="6"/>
     </row>
@@ -3640,7 +3946,7 @@
         <v>57</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>189</v>
@@ -3663,7 +3969,7 @@
         <v>192</v>
       </c>
       <c r="F85" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>193</v>
@@ -3686,7 +3992,7 @@
         <v>192</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G86" s="4"/>
     </row>
@@ -3707,7 +4013,7 @@
         <v>192</v>
       </c>
       <c r="F87" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G87" s="6"/>
     </row>
@@ -3728,7 +4034,7 @@
         <v>192</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G88" s="4"/>
     </row>
@@ -3749,7 +4055,7 @@
         <v>192</v>
       </c>
       <c r="F89" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G89" s="6"/>
     </row>
@@ -3770,7 +4076,7 @@
         <v>192</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G90" s="4"/>
     </row>
@@ -3791,7 +4097,7 @@
         <v>192</v>
       </c>
       <c r="F91" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G91" s="6"/>
     </row>
@@ -3812,7 +4118,7 @@
         <v>208</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>209</v>
@@ -3835,7 +4141,7 @@
         <v>208</v>
       </c>
       <c r="F93" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G93" s="6"/>
     </row>
@@ -3856,7 +4162,7 @@
         <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G94" s="4"/>
     </row>
@@ -3877,7 +4183,7 @@
         <v>208</v>
       </c>
       <c r="F95" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G95" s="6"/>
     </row>
@@ -3898,7 +4204,7 @@
         <v>208</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>217</v>
@@ -3921,7 +4227,7 @@
         <v>208</v>
       </c>
       <c r="F97" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G97" s="6"/>
     </row>
@@ -3942,7 +4248,7 @@
         <v>221</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>222</v>
@@ -3965,7 +4271,7 @@
         <v>221</v>
       </c>
       <c r="F99" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G99" s="6" t="s">
         <v>225</v>
@@ -3988,7 +4294,7 @@
         <v>221</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>228</v>
@@ -4011,7 +4317,7 @@
         <v>231</v>
       </c>
       <c r="F101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G101" s="6"/>
     </row>
@@ -4032,7 +4338,7 @@
         <v>231</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>234</v>
@@ -4055,7 +4361,7 @@
         <v>231</v>
       </c>
       <c r="F103" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G103" s="6"/>
     </row>
@@ -4076,7 +4382,7 @@
         <v>180</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G104" s="4"/>
     </row>
@@ -4097,7 +4403,7 @@
         <v>192</v>
       </c>
       <c r="F105" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G105" s="6"/>
     </row>
@@ -4118,7 +4424,7 @@
         <v>243</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G106" s="4"/>
     </row>
@@ -4139,7 +4445,7 @@
         <v>101</v>
       </c>
       <c r="F107" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G107" s="6"/>
     </row>
@@ -4154,13 +4460,13 @@
         <v>1620</v>
       </c>
       <c r="D108" s="3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>57</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G108" s="4"/>
     </row>
@@ -4181,7 +4487,7 @@
         <v>273</v>
       </c>
       <c r="F109" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G109" s="6"/>
     </row>
@@ -4202,7 +4508,7 @@
         <v>22</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G110" s="4"/>
     </row>
@@ -4223,7 +4529,7 @@
         <v>243</v>
       </c>
       <c r="F111" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G111" s="6"/>
     </row>
@@ -4244,7 +4550,7 @@
         <v>180</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G112" s="4"/>
     </row>
@@ -4265,7 +4571,7 @@
         <v>101</v>
       </c>
       <c r="F113" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G113" s="6"/>
     </row>
@@ -4286,7 +4592,7 @@
         <v>265</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G114" s="4"/>
     </row>
@@ -4307,7 +4613,7 @@
         <v>265</v>
       </c>
       <c r="F115" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -4327,7 +4633,7 @@
         <v>277</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G116" s="4"/>
     </row>
@@ -4348,7 +4654,7 @@
         <v>266</v>
       </c>
       <c r="F117" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -4368,7 +4674,7 @@
         <v>270</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>269</v>
@@ -4391,7 +4697,7 @@
         <v>9</v>
       </c>
       <c r="F119" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -4411,7 +4717,7 @@
         <v>277</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G120" s="4"/>
     </row>
@@ -4432,7 +4738,7 @@
         <v>277</v>
       </c>
       <c r="F121" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -4452,7 +4758,7 @@
         <v>48</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G122" s="4" t="s">
         <v>282</v>
@@ -4475,7 +4781,7 @@
         <v>48</v>
       </c>
       <c r="F123" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -4495,7 +4801,7 @@
         <v>48</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G124" s="4"/>
     </row>
@@ -4516,7 +4822,7 @@
         <v>48</v>
       </c>
       <c r="F125" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -4536,7 +4842,7 @@
         <v>48</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>289</v>
@@ -4559,7 +4865,7 @@
         <v>294</v>
       </c>
       <c r="F127" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G127" t="s">
         <v>292</v>
@@ -4582,7 +4888,7 @@
         <v>16</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G128" s="4"/>
     </row>
@@ -4603,7 +4909,7 @@
         <v>57</v>
       </c>
       <c r="F129" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>297</v>
@@ -4626,10 +4932,10 @@
         <v>57</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>300</v>
+        <v>470</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -4649,18 +4955,18 @@
         <v>57</v>
       </c>
       <c r="F131" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G131" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="C132" s="3">
         <v>1800</v>
@@ -4672,16 +4978,16 @@
         <v>101</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G132" s="4"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B133" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C133" s="5">
         <v>1798</v>
@@ -4693,15 +4999,15 @@
         <v>101</v>
       </c>
       <c r="F133" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="C134" s="3">
         <v>1811</v>
@@ -4713,18 +5019,18 @@
         <v>101</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C135" s="5">
         <v>1827</v>
@@ -4736,15 +5042,15 @@
         <v>101</v>
       </c>
       <c r="F135" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G135" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>23</v>
@@ -4759,16 +5065,16 @@
         <v>24</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G136" s="4"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>310</v>
+      </c>
+      <c r="B137" t="s">
         <v>311</v>
-      </c>
-      <c r="B137" t="s">
-        <v>312</v>
       </c>
       <c r="C137" s="5">
         <v>1886</v>
@@ -4777,92 +5083,1684 @@
         <v>3.5</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F137" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="2"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="4"/>
-      <c r="F138" s="2"/>
+      <c r="A138" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C138" s="3">
+        <v>1810</v>
+      </c>
+      <c r="D138" s="3">
+        <v>3</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>449</v>
+      </c>
       <c r="G138" s="4"/>
     </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>453</v>
+      </c>
+      <c r="B139" t="s">
+        <v>454</v>
+      </c>
+      <c r="C139" s="5">
+        <v>1841</v>
+      </c>
+      <c r="D139" s="5">
+        <v>4</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F139" t="s">
+        <v>452</v>
+      </c>
+    </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="2"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
-      <c r="E140" s="4"/>
-      <c r="F140" s="2"/>
+      <c r="A140" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C140" s="3">
+        <v>1814</v>
+      </c>
+      <c r="D140" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>455</v>
+      </c>
       <c r="G140" s="4"/>
     </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>458</v>
+      </c>
+      <c r="B141" t="s">
+        <v>459</v>
+      </c>
+      <c r="C141" s="5">
+        <v>1860</v>
+      </c>
+      <c r="D141" s="5">
+        <v>4</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F141" t="s">
+        <v>457</v>
+      </c>
+    </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="2"/>
-      <c r="B142" s="2"/>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="4"/>
-      <c r="F142" s="2"/>
+      <c r="A142" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C142" s="3">
+        <v>1897</v>
+      </c>
+      <c r="D142" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>460</v>
+      </c>
       <c r="G142" s="4"/>
     </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>464</v>
+      </c>
+      <c r="B143" t="s">
+        <v>465</v>
+      </c>
+      <c r="C143" s="5">
+        <v>1905</v>
+      </c>
+      <c r="D143" s="5">
+        <v>3</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F143" t="s">
+        <v>463</v>
+      </c>
+    </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="2"/>
-      <c r="B144" s="2"/>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
-      <c r="E144" s="4"/>
-      <c r="F144" s="2"/>
+      <c r="A144" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C144" s="3">
+        <v>1889</v>
+      </c>
+      <c r="D144" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>468</v>
+      </c>
       <c r="G144" s="4"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="2"/>
-      <c r="B146" s="2"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="4"/>
-      <c r="F146" s="2"/>
-      <c r="G146" s="4"/>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>471</v>
+      </c>
+      <c r="B145" t="s">
+        <v>472</v>
+      </c>
+      <c r="C145" s="5">
+        <v>1913</v>
+      </c>
+      <c r="D145" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F145" t="s">
+        <v>474</v>
+      </c>
+      <c r="G145" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C146" s="3">
+        <v>1917</v>
+      </c>
+      <c r="D146" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>480</v>
+      </c>
+      <c r="B147" t="s">
+        <v>253</v>
+      </c>
+      <c r="C147" s="5">
+        <v>1928</v>
+      </c>
+      <c r="D147" s="5">
+        <v>3</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F147" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="2"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="4"/>
-      <c r="F148" s="2"/>
+      <c r="A148" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C148" s="3">
+        <v>1939</v>
+      </c>
+      <c r="D148" s="3">
+        <v>2</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>484</v>
+      </c>
       <c r="G148" s="4"/>
     </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>485</v>
+      </c>
+      <c r="B149" t="s">
+        <v>486</v>
+      </c>
+      <c r="C149" s="5">
+        <v>1921</v>
+      </c>
+      <c r="D149" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F149" t="s">
+        <v>487</v>
+      </c>
+    </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="2"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="3"/>
-      <c r="D150" s="3"/>
-      <c r="E150" s="4"/>
-      <c r="F150" s="2"/>
+      <c r="A150" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C150" s="3">
+        <v>2016</v>
+      </c>
+      <c r="D150" s="3">
+        <v>4</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>490</v>
+      </c>
       <c r="G150" s="4"/>
     </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>492</v>
+      </c>
+      <c r="B151" t="s">
+        <v>491</v>
+      </c>
+      <c r="C151" s="5">
+        <v>2021</v>
+      </c>
+      <c r="D151" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F151" t="s">
+        <v>494</v>
+      </c>
+    </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="2"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="4"/>
-      <c r="F152" s="2"/>
+      <c r="A152" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C152" s="3">
+        <v>2018</v>
+      </c>
+      <c r="D152" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>497</v>
+      </c>
       <c r="G152" s="4"/>
     </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>507</v>
+      </c>
+      <c r="B153" t="s">
+        <v>495</v>
+      </c>
+      <c r="C153" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D153" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F153" t="s">
+        <v>498</v>
+      </c>
+    </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="2"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="4"/>
-      <c r="F154" s="2"/>
+      <c r="A154" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C154" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D154" s="3">
+        <v>4</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>500</v>
+      </c>
       <c r="G154" s="4"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>501</v>
+      </c>
+      <c r="B155" t="s">
+        <v>502</v>
+      </c>
+      <c r="C155" s="5">
+        <v>2020</v>
+      </c>
+      <c r="D155" s="5">
+        <v>3</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F155" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C156" s="3">
+        <v>2022</v>
+      </c>
+      <c r="D156" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>510</v>
+      </c>
+      <c r="B157" t="s">
+        <v>509</v>
+      </c>
+      <c r="C157" s="5">
+        <v>2016</v>
+      </c>
+      <c r="D157" s="5">
+        <v>3</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="F157" t="s">
+        <v>512</v>
+      </c>
+      <c r="G157" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C158" s="3">
+        <v>1923</v>
+      </c>
+      <c r="D158" s="3">
+        <v>3</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="G158" s="4"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>518</v>
+      </c>
+      <c r="B159" t="s">
+        <v>515</v>
+      </c>
+      <c r="C159" s="5">
+        <v>1926</v>
+      </c>
+      <c r="D159" s="5">
+        <v>3</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F159" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C160" s="3">
+        <v>1966</v>
+      </c>
+      <c r="D160" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>523</v>
+      </c>
+      <c r="B161" t="s">
+        <v>524</v>
+      </c>
+      <c r="C161" s="5">
+        <v>1980</v>
+      </c>
+      <c r="D161" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F161" t="s">
+        <v>525</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C162" s="3">
+        <v>1999</v>
+      </c>
+      <c r="D162" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E162" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>531</v>
+      </c>
+      <c r="B163" t="s">
+        <v>532</v>
+      </c>
+      <c r="C163" s="5">
+        <v>1968</v>
+      </c>
+      <c r="D163" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="F163" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C164" s="3">
+        <v>1923</v>
+      </c>
+      <c r="D164" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="E164" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="G164" s="4"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>539</v>
+      </c>
+      <c r="B165" t="s">
+        <v>541</v>
+      </c>
+      <c r="C165" s="5">
+        <v>1992</v>
+      </c>
+      <c r="D165" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="F165" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C166" s="3">
+        <v>1810</v>
+      </c>
+      <c r="D166" s="3">
+        <v>4</v>
+      </c>
+      <c r="E166" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="G166" s="4"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>544</v>
+      </c>
+      <c r="B167" t="s">
+        <v>545</v>
+      </c>
+      <c r="C167" s="5">
+        <v>1884</v>
+      </c>
+      <c r="D167" s="5">
+        <v>3</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C168" s="3">
+        <v>1911</v>
+      </c>
+      <c r="D168" s="3">
+        <v>4</v>
+      </c>
+      <c r="E168" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="G168" s="4"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>547</v>
+      </c>
+      <c r="B169" t="s">
+        <v>545</v>
+      </c>
+      <c r="C169" s="5">
+        <v>1885</v>
+      </c>
+      <c r="D169" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="4"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C171" s="5"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="6"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="4"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="6"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="4"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="4"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C176" s="5"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="6"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="4"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C178" s="5"/>
+      <c r="D178" s="5"/>
+      <c r="E178" s="6"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="2"/>
+      <c r="G179" s="4"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C180" s="5"/>
+      <c r="D180" s="5"/>
+      <c r="E180" s="6"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="4"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C182" s="5"/>
+      <c r="D182" s="5"/>
+      <c r="E182" s="6"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="2"/>
+      <c r="G183" s="4"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C184" s="5"/>
+      <c r="D184" s="5"/>
+      <c r="E184" s="6"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="2"/>
+      <c r="G185" s="4"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C186" s="5"/>
+      <c r="D186" s="5"/>
+      <c r="E186" s="6"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="2"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="2"/>
+      <c r="G187" s="4"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C188" s="5"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="6"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="2"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="2"/>
+      <c r="G189" s="4"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="2"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="2"/>
+      <c r="G190" s="4"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="6"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="2"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="2"/>
+      <c r="G192" s="4"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C193" s="5"/>
+      <c r="D193" s="5"/>
+      <c r="E193" s="6"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="2"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="4"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C195" s="5"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="6"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="2"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="2"/>
+      <c r="G196" s="4"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C197" s="5"/>
+      <c r="D197" s="5"/>
+      <c r="E197" s="6"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="2"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="2"/>
+      <c r="G198" s="4"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C199" s="5"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="6"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="2"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="4"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C201" s="5"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="6"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="2"/>
+      <c r="B202" s="2"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="2"/>
+      <c r="G202" s="4"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="6"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="2"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="4"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="4"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="2"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="4"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C206" s="5"/>
+      <c r="D206" s="5"/>
+      <c r="E206" s="6"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+      <c r="E207" s="4"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="4"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C208" s="5"/>
+      <c r="D208" s="5"/>
+      <c r="E208" s="6"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="2"/>
+      <c r="B209" s="2"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="4"/>
+      <c r="F209" s="2"/>
+      <c r="G209" s="4"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C210" s="5"/>
+      <c r="D210" s="5"/>
+      <c r="E210" s="6"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="2"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
+      <c r="E211" s="4"/>
+      <c r="F211" s="2"/>
+      <c r="G211" s="4"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C212" s="5"/>
+      <c r="D212" s="5"/>
+      <c r="E212" s="6"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
+      <c r="E213" s="4"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="4"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C214" s="5"/>
+      <c r="D214" s="5"/>
+      <c r="E214" s="6"/>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="4"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="4"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C216" s="5"/>
+      <c r="D216" s="5"/>
+      <c r="E216" s="6"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
+      <c r="E217" s="4"/>
+      <c r="F217" s="2"/>
+      <c r="G217" s="4"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C218" s="5"/>
+      <c r="D218" s="5"/>
+      <c r="E218" s="6"/>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
+      <c r="E219" s="4"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="4"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="4"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C221" s="5"/>
+      <c r="D221" s="5"/>
+      <c r="E221" s="6"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
+      <c r="E222" s="4"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="4"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C223" s="5"/>
+      <c r="D223" s="5"/>
+      <c r="E223" s="6"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="4"/>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C225" s="5"/>
+      <c r="D225" s="5"/>
+      <c r="E225" s="6"/>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="2"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
+      <c r="E226" s="4"/>
+      <c r="F226" s="2"/>
+      <c r="G226" s="4"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C227" s="5"/>
+      <c r="D227" s="5"/>
+      <c r="E227" s="6"/>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="2"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
+      <c r="E228" s="4"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="4"/>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C229" s="5"/>
+      <c r="D229" s="5"/>
+      <c r="E229" s="6"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="2"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
+      <c r="E230" s="4"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="4"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C231" s="5"/>
+      <c r="D231" s="5"/>
+      <c r="E231" s="6"/>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
+      <c r="E232" s="4"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="4"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C233" s="5"/>
+      <c r="D233" s="5"/>
+      <c r="E233" s="6"/>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="2"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
+      <c r="E234" s="4"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="4"/>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
+      <c r="E235" s="4"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="4"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C236" s="5"/>
+      <c r="D236" s="5"/>
+      <c r="E236" s="6"/>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="4"/>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C238" s="5"/>
+      <c r="D238" s="5"/>
+      <c r="E238" s="6"/>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
+      <c r="E239" s="4"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="4"/>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C240" s="5"/>
+      <c r="D240" s="5"/>
+      <c r="E240" s="6"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
+      <c r="E241" s="4"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="4"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C242" s="5"/>
+      <c r="D242" s="5"/>
+      <c r="E242" s="6"/>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
+      <c r="E243" s="4"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="4"/>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C244" s="5"/>
+      <c r="D244" s="5"/>
+      <c r="E244" s="6"/>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="3"/>
+      <c r="D245" s="3"/>
+      <c r="E245" s="4"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="4"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C246" s="5"/>
+      <c r="D246" s="5"/>
+      <c r="E246" s="6"/>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="3"/>
+      <c r="D247" s="3"/>
+      <c r="E247" s="4"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="4"/>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C248" s="5"/>
+      <c r="D248" s="5"/>
+      <c r="E248" s="6"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3"/>
+      <c r="E249" s="4"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="4"/>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="4"/>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C251" s="5"/>
+      <c r="D251" s="5"/>
+      <c r="E251" s="6"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="3"/>
+      <c r="D252" s="3"/>
+      <c r="E252" s="4"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="4"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C253" s="5"/>
+      <c r="D253" s="5"/>
+      <c r="E253" s="6"/>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="3"/>
+      <c r="D254" s="3"/>
+      <c r="E254" s="4"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="4"/>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C255" s="5"/>
+      <c r="D255" s="5"/>
+      <c r="E255" s="6"/>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
+      <c r="E256" s="4"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="4"/>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C257" s="5"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="6"/>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="2"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="3"/>
+      <c r="D258" s="3"/>
+      <c r="E258" s="4"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="4"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C259" s="5"/>
+      <c r="D259" s="5"/>
+      <c r="E259" s="6"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="2"/>
+      <c r="B260" s="2"/>
+      <c r="C260" s="3"/>
+      <c r="D260" s="3"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="4"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C261" s="5"/>
+      <c r="D261" s="5"/>
+      <c r="E261" s="6"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" s="2"/>
+      <c r="B262" s="2"/>
+      <c r="C262" s="3"/>
+      <c r="D262" s="3"/>
+      <c r="E262" s="4"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="4"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C263" s="5"/>
+      <c r="D263" s="5"/>
+      <c r="E263" s="6"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" s="2"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="3"/>
+      <c r="D264" s="3"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="4"/>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" s="2"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="3"/>
+      <c r="E265" s="4"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="4"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C266" s="5"/>
+      <c r="D266" s="5"/>
+      <c r="E266" s="6"/>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="2"/>
+      <c r="B267" s="2"/>
+      <c r="C267" s="3"/>
+      <c r="D267" s="3"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="2"/>
+      <c r="G267" s="4"/>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C268" s="5"/>
+      <c r="D268" s="5"/>
+      <c r="E268" s="6"/>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="3"/>
+      <c r="D269" s="3"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="4"/>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C270" s="5"/>
+      <c r="D270" s="5"/>
+      <c r="E270" s="6"/>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="2"/>
+      <c r="B271" s="2"/>
+      <c r="C271" s="3"/>
+      <c r="D271" s="3"/>
+      <c r="E271" s="4"/>
+      <c r="F271" s="2"/>
+      <c r="G271" s="4"/>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C272" s="5"/>
+      <c r="D272" s="5"/>
+      <c r="E272" s="6"/>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" s="2"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="3"/>
+      <c r="D273" s="3"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="4"/>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C274" s="5"/>
+      <c r="D274" s="5"/>
+      <c r="E274" s="6"/>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" s="2"/>
+      <c r="B275" s="2"/>
+      <c r="C275" s="3"/>
+      <c r="D275" s="3"/>
+      <c r="E275" s="4"/>
+      <c r="F275" s="2"/>
+      <c r="G275" s="4"/>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C276" s="5"/>
+      <c r="D276" s="5"/>
+      <c r="E276" s="6"/>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" s="2"/>
+      <c r="B277" s="2"/>
+      <c r="C277" s="3"/>
+      <c r="D277" s="3"/>
+      <c r="E277" s="4"/>
+      <c r="F277" s="2"/>
+      <c r="G277" s="4"/>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C278" s="5"/>
+      <c r="D278" s="5"/>
+      <c r="E278" s="6"/>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="2"/>
+      <c r="B279" s="2"/>
+      <c r="C279" s="3"/>
+      <c r="D279" s="3"/>
+      <c r="E279" s="4"/>
+      <c r="F279" s="2"/>
+      <c r="G279" s="4"/>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="2"/>
+      <c r="B280" s="2"/>
+      <c r="C280" s="3"/>
+      <c r="D280" s="3"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="2"/>
+      <c r="G280" s="4"/>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C281" s="5"/>
+      <c r="D281" s="5"/>
+      <c r="E281" s="6"/>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282" s="2"/>
+      <c r="B282" s="2"/>
+      <c r="C282" s="3"/>
+      <c r="D282" s="3"/>
+      <c r="E282" s="4"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="4"/>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C283" s="5"/>
+      <c r="D283" s="5"/>
+      <c r="E283" s="6"/>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" s="2"/>
+      <c r="B284" s="2"/>
+      <c r="C284" s="3"/>
+      <c r="D284" s="3"/>
+      <c r="E284" s="4"/>
+      <c r="F284" s="2"/>
+      <c r="G284" s="4"/>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C285" s="5"/>
+      <c r="D285" s="5"/>
+      <c r="E285" s="6"/>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="2"/>
+      <c r="B286" s="2"/>
+      <c r="C286" s="3"/>
+      <c r="D286" s="3"/>
+      <c r="E286" s="4"/>
+      <c r="F286" s="2"/>
+      <c r="G286" s="4"/>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C287" s="5"/>
+      <c r="D287" s="5"/>
+      <c r="E287" s="6"/>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="2"/>
+      <c r="B288" s="2"/>
+      <c r="C288" s="3"/>
+      <c r="D288" s="3"/>
+      <c r="E288" s="4"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="4"/>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C289" s="5"/>
+      <c r="D289" s="5"/>
+      <c r="E289" s="6"/>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290" s="2"/>
+      <c r="B290" s="2"/>
+      <c r="C290" s="3"/>
+      <c r="D290" s="3"/>
+      <c r="E290" s="4"/>
+      <c r="F290" s="2"/>
+      <c r="G290" s="4"/>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C291" s="5"/>
+      <c r="D291" s="5"/>
+      <c r="E291" s="6"/>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A292" s="2"/>
+      <c r="B292" s="2"/>
+      <c r="C292" s="3"/>
+      <c r="D292" s="3"/>
+      <c r="E292" s="4"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="4"/>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C293" s="5"/>
+      <c r="D293" s="5"/>
+      <c r="E293" s="6"/>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A294" s="2"/>
+      <c r="B294" s="2"/>
+      <c r="C294" s="3"/>
+      <c r="D294" s="3"/>
+      <c r="E294" s="4"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="4"/>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A295" s="2"/>
+      <c r="B295" s="2"/>
+      <c r="C295" s="3"/>
+      <c r="D295" s="3"/>
+      <c r="E295" s="4"/>
+      <c r="F295" s="2"/>
+      <c r="G295" s="4"/>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C296" s="5"/>
+      <c r="D296" s="5"/>
+      <c r="E296" s="6"/>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A297" s="2"/>
+      <c r="B297" s="2"/>
+      <c r="C297" s="3"/>
+      <c r="D297" s="3"/>
+      <c r="E297" s="4"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="4"/>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C298" s="5"/>
+      <c r="D298" s="5"/>
+      <c r="E298" s="6"/>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
+      <c r="C299" s="3"/>
+      <c r="D299" s="3"/>
+      <c r="E299" s="4"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="4"/>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C300" s="5"/>
+      <c r="D300" s="5"/>
+      <c r="E300" s="6"/>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301" s="2"/>
+      <c r="B301" s="2"/>
+      <c r="C301" s="3"/>
+      <c r="D301" s="3"/>
+      <c r="E301" s="4"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="4"/>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C302" s="5"/>
+      <c r="D302" s="5"/>
+      <c r="E302" s="6"/>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303" s="2"/>
+      <c r="B303" s="2"/>
+      <c r="C303" s="3"/>
+      <c r="D303" s="3"/>
+      <c r="E303" s="4"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="4"/>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C304" s="5"/>
+      <c r="D304" s="5"/>
+      <c r="E304" s="6"/>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305" s="2"/>
+      <c r="B305" s="2"/>
+      <c r="C305" s="3"/>
+      <c r="D305" s="3"/>
+      <c r="E305" s="4"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="4"/>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C306" s="5"/>
+      <c r="D306" s="5"/>
+      <c r="E306" s="6"/>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307" s="2"/>
+      <c r="B307" s="2"/>
+      <c r="C307" s="3"/>
+      <c r="D307" s="3"/>
+      <c r="E307" s="4"/>
+      <c r="F307" s="2"/>
+      <c r="G307" s="4"/>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C308" s="5"/>
+      <c r="D308" s="5"/>
+      <c r="E308" s="6"/>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="2"/>
+      <c r="B309" s="2"/>
+      <c r="C309" s="3"/>
+      <c r="D309" s="3"/>
+      <c r="E309" s="4"/>
+      <c r="F309" s="2"/>
+      <c r="G309" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
